--- a/init_db_scripts/sources/SystemTypes_KII.xlsx
+++ b/init_db_scripts/sources/SystemTypes_KII.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/artemkucher/PycharmProjects/automated-threats-model/init_db_scripts/sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49594FF3-A879-B445-B3E5-4EEB50E77538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7D8685-658E-6040-A01B-F2CC5960C1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20200" activeTab="1" xr2:uid="{1860FBF2-3CEE-734C-8278-C041533F86CB}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20200" xr2:uid="{1860FBF2-3CEE-734C-8278-C041533F86CB}"/>
   </bookViews>
   <sheets>
     <sheet name="KII" sheetId="1" r:id="rId1"/>
@@ -787,7 +787,7 @@
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D13" s="2"/>
@@ -799,7 +799,7 @@
       <c r="B14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="2"/>
@@ -811,7 +811,7 @@
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="2"/>
@@ -823,7 +823,7 @@
       <c r="B16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="2"/>
@@ -835,7 +835,7 @@
       <c r="B17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D17" s="2"/>
@@ -847,7 +847,7 @@
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="2"/>
@@ -859,7 +859,7 @@
       <c r="B19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D19" s="2"/>
@@ -871,7 +871,7 @@
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D20" s="2"/>
@@ -883,7 +883,7 @@
       <c r="B21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D21" s="2"/>
@@ -895,7 +895,7 @@
       <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D22" s="2"/>
@@ -907,7 +907,7 @@
       <c r="B23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D23" s="2"/>
@@ -919,7 +919,7 @@
       <c r="B24" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D24" s="2"/>
@@ -931,7 +931,7 @@
       <c r="B25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D25" s="2"/>
@@ -943,7 +943,7 @@
       <c r="B26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D26" s="2"/>
@@ -955,7 +955,7 @@
       <c r="B27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="2"/>
@@ -967,7 +967,7 @@
       <c r="B28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D28" s="2"/>
@@ -979,7 +979,7 @@
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D29" s="2"/>
@@ -991,7 +991,7 @@
       <c r="B30" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D30" s="2"/>
@@ -1003,7 +1003,7 @@
       <c r="B31" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D31" s="2"/>
@@ -1015,7 +1015,7 @@
       <c r="B32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D32" s="2"/>
@@ -1027,7 +1027,7 @@
       <c r="B33" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="2"/>
@@ -1039,7 +1039,7 @@
       <c r="B34" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>57</v>
       </c>
       <c r="D34" s="2"/>
@@ -1051,7 +1051,7 @@
       <c r="B35" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D35" s="2"/>
@@ -1063,7 +1063,7 @@
       <c r="B36" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D36" s="2"/>
@@ -1075,7 +1075,7 @@
       <c r="B37" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D37" s="2"/>
@@ -1087,7 +1087,7 @@
       <c r="B38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D38" s="2"/>
@@ -1099,7 +1099,7 @@
       <c r="B39" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D39" s="2"/>
@@ -1111,7 +1111,7 @@
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D40" s="2"/>
@@ -1123,7 +1123,7 @@
       <c r="B41" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D41" s="2"/>
@@ -1135,7 +1135,7 @@
       <c r="B42" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D42" s="2"/>
@@ -1147,7 +1147,7 @@
       <c r="B43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D43" s="2"/>
@@ -1159,7 +1159,7 @@
       <c r="B44" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D44" s="2"/>
@@ -1171,7 +1171,7 @@
       <c r="B45" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="3" t="s">
         <v>58</v>
       </c>
       <c r="D45" s="2"/>
@@ -10967,7097 +10967,7097 @@
     </row>
     <row r="398" spans="1:14">
       <c r="A398" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A2, ",", B2, ");")</f>
+        <f t="shared" ref="A398:A461" si="0">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A2, ",", B2, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,12);</v>
       </c>
       <c r="E398" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E2, ",", F2, ");")</f>
+        <f t="shared" ref="E398:E461" si="1">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E2, ",", F2, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,12);</v>
       </c>
       <c r="I398" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I2, ",", J2, ");")</f>
+        <f t="shared" ref="I398:I461" si="2">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I2, ",", J2, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,12);</v>
       </c>
       <c r="M398" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M2, ",", N2, ");")</f>
+        <f t="shared" ref="M398:M461" si="3">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M2, ",", N2, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,12);</v>
       </c>
     </row>
     <row r="399" spans="1:14">
       <c r="A399" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A3, ",", B3, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,14);</v>
       </c>
       <c r="E399" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E3, ",", F3, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,14);</v>
       </c>
       <c r="I399" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I3, ",", J3, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,14);</v>
       </c>
       <c r="M399" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M3, ",", N3, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,14);</v>
       </c>
     </row>
     <row r="400" spans="1:14">
       <c r="A400" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A4, ",", B4, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,15);</v>
       </c>
       <c r="E400" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E4, ",", F4, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,15);</v>
       </c>
       <c r="I400" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I4, ",", J4, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,15);</v>
       </c>
       <c r="M400" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M4, ",", N4, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,15);</v>
       </c>
     </row>
     <row r="401" spans="1:13">
       <c r="A401" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A5, ",", B5, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,16);</v>
       </c>
       <c r="E401" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E5, ",", F5, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,16);</v>
       </c>
       <c r="I401" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I5, ",", J5, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,16);</v>
       </c>
       <c r="M401" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M5, ",", N5, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,16);</v>
       </c>
     </row>
     <row r="402" spans="1:13">
       <c r="A402" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A6, ",", B6, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,18);</v>
       </c>
       <c r="E402" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E6, ",", F6, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,18);</v>
       </c>
       <c r="I402" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I6, ",", J6, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,18);</v>
       </c>
       <c r="M402" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M6, ",", N6, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,18);</v>
       </c>
     </row>
     <row r="403" spans="1:13">
       <c r="A403" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A7, ",", B7, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,19);</v>
       </c>
       <c r="E403" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E7, ",", F7, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,19);</v>
       </c>
       <c r="I403" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I7, ",", J7, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,19);</v>
       </c>
       <c r="M403" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M7, ",", N7, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,19);</v>
       </c>
     </row>
     <row r="404" spans="1:13">
       <c r="A404" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A8, ",", B8, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,20);</v>
       </c>
       <c r="E404" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E8, ",", F8, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,20);</v>
       </c>
       <c r="I404" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I8, ",", J8, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,20);</v>
       </c>
       <c r="M404" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M8, ",", N8, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,20);</v>
       </c>
     </row>
     <row r="405" spans="1:13">
       <c r="A405" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A9, ",", B9, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,21);</v>
       </c>
       <c r="E405" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E9, ",", F9, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,21);</v>
       </c>
       <c r="I405" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I9, ",", J9, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,21);</v>
       </c>
       <c r="M405" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M9, ",", N9, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,21);</v>
       </c>
     </row>
     <row r="406" spans="1:13">
       <c r="A406" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A10, ",", B10, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,22);</v>
       </c>
       <c r="E406" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E10, ",", F10, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,22);</v>
       </c>
       <c r="I406" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I10, ",", J10, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,22);</v>
       </c>
       <c r="M406" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M10, ",", N10, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,22);</v>
       </c>
     </row>
     <row r="407" spans="1:13">
       <c r="A407" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A11, ",", B11, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,23);</v>
       </c>
       <c r="E407" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E11, ",", F11, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,23);</v>
       </c>
       <c r="I407" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I11, ",", J11, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,23);</v>
       </c>
       <c r="M407" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M11, ",", N11, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,23);</v>
       </c>
     </row>
     <row r="408" spans="1:13">
       <c r="A408" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A12, ",", B12, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,24);</v>
       </c>
       <c r="E408" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E12, ",", F12, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,24);</v>
       </c>
       <c r="I408" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I12, ",", J12, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,24);</v>
       </c>
       <c r="M408" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M12, ",", N12, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,24);</v>
       </c>
     </row>
     <row r="409" spans="1:13">
       <c r="A409" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A13, ",", B13, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,25);</v>
       </c>
       <c r="E409" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E13, ",", F13, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,25);</v>
       </c>
       <c r="I409" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I13, ",", J13, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,25);</v>
       </c>
       <c r="M409" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M13, ",", N13, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,25);</v>
       </c>
     </row>
     <row r="410" spans="1:13">
       <c r="A410" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A14, ",", B14, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,26);</v>
       </c>
       <c r="E410" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E14, ",", F14, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,26);</v>
       </c>
       <c r="I410" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I14, ",", J14, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,26);</v>
       </c>
       <c r="M410" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M14, ",", N14, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,26);</v>
       </c>
     </row>
     <row r="411" spans="1:13">
       <c r="A411" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A15, ",", B15, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,27);</v>
       </c>
       <c r="E411" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E15, ",", F15, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,27);</v>
       </c>
       <c r="I411" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I15, ",", J15, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,27);</v>
       </c>
       <c r="M411" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M15, ",", N15, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,27);</v>
       </c>
     </row>
     <row r="412" spans="1:13">
       <c r="A412" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A16, ",", B16, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,28);</v>
       </c>
       <c r="E412" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E16, ",", F16, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,28);</v>
       </c>
       <c r="I412" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I16, ",", J16, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,28);</v>
       </c>
       <c r="M412" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M16, ",", N16, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,28);</v>
       </c>
     </row>
     <row r="413" spans="1:13">
       <c r="A413" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A17, ",", B17, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,29);</v>
       </c>
       <c r="E413" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E17, ",", F17, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,29);</v>
       </c>
       <c r="I413" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I17, ",", J17, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,29);</v>
       </c>
       <c r="M413" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M17, ",", N17, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,29);</v>
       </c>
     </row>
     <row r="414" spans="1:13">
       <c r="A414" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A18, ",", B18, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,30);</v>
       </c>
       <c r="E414" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E18, ",", F18, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,30);</v>
       </c>
       <c r="I414" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I18, ",", J18, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,30);</v>
       </c>
       <c r="M414" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M18, ",", N18, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,30);</v>
       </c>
     </row>
     <row r="415" spans="1:13">
       <c r="A415" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A19, ",", B19, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,31);</v>
       </c>
       <c r="E415" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E19, ",", F19, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,31);</v>
       </c>
       <c r="I415" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I19, ",", J19, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,31);</v>
       </c>
       <c r="M415" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M19, ",", N19, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,31);</v>
       </c>
     </row>
     <row r="416" spans="1:13">
       <c r="A416" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A20, ",", B20, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,32);</v>
       </c>
       <c r="E416" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E20, ",", F20, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,32);</v>
       </c>
       <c r="I416" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I20, ",", J20, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,32);</v>
       </c>
       <c r="M416" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M20, ",", N20, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,32);</v>
       </c>
     </row>
     <row r="417" spans="1:13">
       <c r="A417" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A21, ",", B21, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,35);</v>
       </c>
       <c r="E417" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E21, ",", F21, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,35);</v>
       </c>
       <c r="I417" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I21, ",", J21, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,35);</v>
       </c>
       <c r="M417" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M21, ",", N21, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,35);</v>
       </c>
     </row>
     <row r="418" spans="1:13">
       <c r="A418" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A22, ",", B22, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,36);</v>
       </c>
       <c r="E418" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E22, ",", F22, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,36);</v>
       </c>
       <c r="I418" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I22, ",", J22, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,36);</v>
       </c>
       <c r="M418" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M22, ",", N22, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,36);</v>
       </c>
     </row>
     <row r="419" spans="1:13">
       <c r="A419" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A23, ",", B23, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,59);</v>
       </c>
       <c r="E419" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E23, ",", F23, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,59);</v>
       </c>
       <c r="I419" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I23, ",", J23, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,59);</v>
       </c>
       <c r="M419" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M23, ",", N23, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,59);</v>
       </c>
     </row>
     <row r="420" spans="1:13">
       <c r="A420" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A24, ",", B24, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,60);</v>
       </c>
       <c r="E420" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E24, ",", F24, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,60);</v>
       </c>
       <c r="I420" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I24, ",", J24, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,60);</v>
       </c>
       <c r="M420" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M24, ",", N24, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,60);</v>
       </c>
     </row>
     <row r="421" spans="1:13">
       <c r="A421" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A25, ",", B25, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,63);</v>
       </c>
       <c r="E421" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E25, ",", F25, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,63);</v>
       </c>
       <c r="I421" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I25, ",", J25, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,63);</v>
       </c>
       <c r="M421" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M25, ",", N25, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,63);</v>
       </c>
     </row>
     <row r="422" spans="1:13">
       <c r="A422" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A26, ",", B26, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (1,65);</v>
       </c>
       <c r="E422" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E26, ",", F26, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,65);</v>
       </c>
       <c r="I422" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I26, ",", J26, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,65);</v>
       </c>
       <c r="M422" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M26, ",", N26, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,65);</v>
       </c>
     </row>
     <row r="423" spans="1:13">
       <c r="A423" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A27, ",", B27, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E423" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E27, ",", F27, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,37);</v>
       </c>
       <c r="I423" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I27, ",", J27, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,37);</v>
       </c>
       <c r="M423" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M27, ",", N27, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,37);</v>
       </c>
     </row>
     <row r="424" spans="1:13">
       <c r="A424" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A28, ",", B28, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E424" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E28, ",", F28, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,38);</v>
       </c>
       <c r="I424" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I28, ",", J28, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,38);</v>
       </c>
       <c r="M424" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M28, ",", N28, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,38);</v>
       </c>
     </row>
     <row r="425" spans="1:13">
       <c r="A425" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A29, ",", B29, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E425" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E29, ",", F29, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,43);</v>
       </c>
       <c r="I425" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I29, ",", J29, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,43);</v>
       </c>
       <c r="M425" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M29, ",", N29, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,43);</v>
       </c>
     </row>
     <row r="426" spans="1:13">
       <c r="A426" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A30, ",", B30, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E426" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E30, ",", F30, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,44);</v>
       </c>
       <c r="I426" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I30, ",", J30, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,44);</v>
       </c>
       <c r="M426" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M30, ",", N30, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,44);</v>
       </c>
     </row>
     <row r="427" spans="1:13">
       <c r="A427" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A31, ",", B31, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E427" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E31, ",", F31, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,45);</v>
       </c>
       <c r="I427" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I31, ",", J31, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,45);</v>
       </c>
       <c r="M427" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M31, ",", N31, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,45);</v>
       </c>
     </row>
     <row r="428" spans="1:13">
       <c r="A428" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A32, ",", B32, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E428" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E32, ",", F32, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,51);</v>
       </c>
       <c r="I428" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I32, ",", J32, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,51);</v>
       </c>
       <c r="M428" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M32, ",", N32, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,51);</v>
       </c>
     </row>
     <row r="429" spans="1:13">
       <c r="A429" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A33, ",", B33, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E429" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E33, ",", F33, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,56);</v>
       </c>
       <c r="I429" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I33, ",", J33, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,56);</v>
       </c>
       <c r="M429" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M33, ",", N33, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,56);</v>
       </c>
     </row>
     <row r="430" spans="1:13">
       <c r="A430" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A34, ",", B34, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E430" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E34, ",", F34, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (2,58);</v>
       </c>
       <c r="I430" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I34, ",", J34, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (3,58);</v>
       </c>
       <c r="M430" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M34, ",", N34, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (4,58);</v>
       </c>
     </row>
     <row r="431" spans="1:13">
       <c r="A431" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A35, ",", B35, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E431" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E35, ",", F35, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I431" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I35, ",", J35, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M431" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M35, ",", N35, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="432" spans="1:13">
       <c r="A432" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A36, ",", B36, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (FINANCIAL,);</v>
       </c>
       <c r="E432" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E36, ",", F36, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I432" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I36, ",", J36, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M432" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M36, ",", N36, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="433" spans="1:13">
       <c r="A433" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A37, ",", B37, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,12);</v>
       </c>
       <c r="E433" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E37, ",", F37, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,12);</v>
       </c>
       <c r="I433" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I37, ",", J37, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,12);</v>
       </c>
       <c r="M433" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M37, ",", N37, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,12);</v>
       </c>
     </row>
     <row r="434" spans="1:13">
       <c r="A434" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A38, ",", B38, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,14);</v>
       </c>
       <c r="E434" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E38, ",", F38, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,14);</v>
       </c>
       <c r="I434" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I38, ",", J38, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,14);</v>
       </c>
       <c r="M434" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M38, ",", N38, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,14);</v>
       </c>
     </row>
     <row r="435" spans="1:13">
       <c r="A435" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A39, ",", B39, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,15);</v>
       </c>
       <c r="E435" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E39, ",", F39, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,15);</v>
       </c>
       <c r="I435" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I39, ",", J39, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,15);</v>
       </c>
       <c r="M435" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M39, ",", N39, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,15);</v>
       </c>
     </row>
     <row r="436" spans="1:13">
       <c r="A436" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A40, ",", B40, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,16);</v>
       </c>
       <c r="E436" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E40, ",", F40, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,16);</v>
       </c>
       <c r="I436" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I40, ",", J40, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,16);</v>
       </c>
       <c r="M436" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M40, ",", N40, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,16);</v>
       </c>
     </row>
     <row r="437" spans="1:13">
       <c r="A437" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A41, ",", B41, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,18);</v>
       </c>
       <c r="E437" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E41, ",", F41, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,18);</v>
       </c>
       <c r="I437" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I41, ",", J41, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,18);</v>
       </c>
       <c r="M437" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M41, ",", N41, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,18);</v>
       </c>
     </row>
     <row r="438" spans="1:13">
       <c r="A438" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A42, ",", B42, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,19);</v>
       </c>
       <c r="E438" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E42, ",", F42, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,19);</v>
       </c>
       <c r="I438" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I42, ",", J42, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,19);</v>
       </c>
       <c r="M438" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M42, ",", N42, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,19);</v>
       </c>
     </row>
     <row r="439" spans="1:13">
       <c r="A439" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A43, ",", B43, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,20);</v>
       </c>
       <c r="E439" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E43, ",", F43, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,20);</v>
       </c>
       <c r="I439" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I43, ",", J43, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,20);</v>
       </c>
       <c r="M439" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M43, ",", N43, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,20);</v>
       </c>
     </row>
     <row r="440" spans="1:13">
       <c r="A440" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A44, ",", B44, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,21);</v>
       </c>
       <c r="E440" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E44, ",", F44, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,21);</v>
       </c>
       <c r="I440" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I44, ",", J44, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,21);</v>
       </c>
       <c r="M440" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M44, ",", N44, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,21);</v>
       </c>
     </row>
     <row r="441" spans="1:13">
       <c r="A441" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A45, ",", B45, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,22);</v>
       </c>
       <c r="E441" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E45, ",", F45, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,22);</v>
       </c>
       <c r="I441" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I45, ",", J45, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,22);</v>
       </c>
       <c r="M441" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M45, ",", N45, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,22);</v>
       </c>
     </row>
     <row r="442" spans="1:13">
       <c r="A442" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A46, ",", B46, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,23);</v>
       </c>
       <c r="E442" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E46, ",", F46, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,23);</v>
       </c>
       <c r="I442" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I46, ",", J46, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,23);</v>
       </c>
       <c r="M442" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M46, ",", N46, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,23);</v>
       </c>
     </row>
     <row r="443" spans="1:13">
       <c r="A443" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A47, ",", B47, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,24);</v>
       </c>
       <c r="E443" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E47, ",", F47, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,24);</v>
       </c>
       <c r="I443" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I47, ",", J47, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,24);</v>
       </c>
       <c r="M443" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M47, ",", N47, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,24);</v>
       </c>
     </row>
     <row r="444" spans="1:13">
       <c r="A444" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A48, ",", B48, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,25);</v>
       </c>
       <c r="E444" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E48, ",", F48, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,25);</v>
       </c>
       <c r="I444" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I48, ",", J48, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,25);</v>
       </c>
       <c r="M444" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M48, ",", N48, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,25);</v>
       </c>
     </row>
     <row r="445" spans="1:13">
       <c r="A445" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A49, ",", B49, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,26);</v>
       </c>
       <c r="E445" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E49, ",", F49, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,26);</v>
       </c>
       <c r="I445" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I49, ",", J49, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,26);</v>
       </c>
       <c r="M445" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M49, ",", N49, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,26);</v>
       </c>
     </row>
     <row r="446" spans="1:13">
       <c r="A446" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A50, ",", B50, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,27);</v>
       </c>
       <c r="E446" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E50, ",", F50, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,27);</v>
       </c>
       <c r="I446" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I50, ",", J50, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,27);</v>
       </c>
       <c r="M446" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M50, ",", N50, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,27);</v>
       </c>
     </row>
     <row r="447" spans="1:13">
       <c r="A447" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A51, ",", B51, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,28);</v>
       </c>
       <c r="E447" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E51, ",", F51, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,28);</v>
       </c>
       <c r="I447" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I51, ",", J51, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,28);</v>
       </c>
       <c r="M447" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M51, ",", N51, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,28);</v>
       </c>
     </row>
     <row r="448" spans="1:13">
       <c r="A448" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A52, ",", B52, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,29);</v>
       </c>
       <c r="E448" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E52, ",", F52, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,29);</v>
       </c>
       <c r="I448" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I52, ",", J52, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,29);</v>
       </c>
       <c r="M448" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M52, ",", N52, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,29);</v>
       </c>
     </row>
     <row r="449" spans="1:13">
       <c r="A449" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A53, ",", B53, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,30);</v>
       </c>
       <c r="E449" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E53, ",", F53, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,30);</v>
       </c>
       <c r="I449" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I53, ",", J53, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,30);</v>
       </c>
       <c r="M449" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M53, ",", N53, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,30);</v>
       </c>
     </row>
     <row r="450" spans="1:13">
       <c r="A450" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A54, ",", B54, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,31);</v>
       </c>
       <c r="E450" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E54, ",", F54, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,31);</v>
       </c>
       <c r="I450" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I54, ",", J54, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,31);</v>
       </c>
       <c r="M450" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M54, ",", N54, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,31);</v>
       </c>
     </row>
     <row r="451" spans="1:13">
       <c r="A451" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A55, ",", B55, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,32);</v>
       </c>
       <c r="E451" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E55, ",", F55, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,32);</v>
       </c>
       <c r="I451" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I55, ",", J55, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,32);</v>
       </c>
       <c r="M451" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M55, ",", N55, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,32);</v>
       </c>
     </row>
     <row r="452" spans="1:13">
       <c r="A452" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A56, ",", B56, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,35);</v>
       </c>
       <c r="E452" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E56, ",", F56, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,35);</v>
       </c>
       <c r="I452" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I56, ",", J56, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,35);</v>
       </c>
       <c r="M452" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M56, ",", N56, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,35);</v>
       </c>
     </row>
     <row r="453" spans="1:13">
       <c r="A453" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A57, ",", B57, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,36);</v>
       </c>
       <c r="E453" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E57, ",", F57, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,36);</v>
       </c>
       <c r="I453" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I57, ",", J57, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,36);</v>
       </c>
       <c r="M453" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M57, ",", N57, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,36);</v>
       </c>
     </row>
     <row r="454" spans="1:13">
       <c r="A454" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A58, ",", B58, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,59);</v>
       </c>
       <c r="E454" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E58, ",", F58, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,59);</v>
       </c>
       <c r="I454" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I58, ",", J58, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,59);</v>
       </c>
       <c r="M454" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M58, ",", N58, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,59);</v>
       </c>
     </row>
     <row r="455" spans="1:13">
       <c r="A455" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A59, ",", B59, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,60);</v>
       </c>
       <c r="E455" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E59, ",", F59, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,60);</v>
       </c>
       <c r="I455" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I59, ",", J59, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,60);</v>
       </c>
       <c r="M455" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M59, ",", N59, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,60);</v>
       </c>
     </row>
     <row r="456" spans="1:13">
       <c r="A456" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A60, ",", B60, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,63);</v>
       </c>
       <c r="E456" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E60, ",", F60, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,63);</v>
       </c>
       <c r="I456" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I60, ",", J60, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,63);</v>
       </c>
       <c r="M456" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M60, ",", N60, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,63);</v>
       </c>
     </row>
     <row r="457" spans="1:13">
       <c r="A457" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A61, ",", B61, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,65);</v>
       </c>
       <c r="E457" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E61, ",", F61, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,65);</v>
       </c>
       <c r="I457" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I61, ",", J61, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,65);</v>
       </c>
       <c r="M457" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M61, ",", N61, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,65);</v>
       </c>
     </row>
     <row r="458" spans="1:13">
       <c r="A458" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A62, ",", B62, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (5,13);</v>
       </c>
       <c r="E458" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E62, ",", F62, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,37);</v>
       </c>
       <c r="I458" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I62, ",", J62, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,37);</v>
       </c>
       <c r="M458" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M62, ",", N62, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,37);</v>
       </c>
     </row>
     <row r="459" spans="1:13">
       <c r="A459" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A63, ",", B63, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E459" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E63, ",", F63, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,38);</v>
       </c>
       <c r="I459" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I63, ",", J63, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,38);</v>
       </c>
       <c r="M459" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M63, ",", N63, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,38);</v>
       </c>
     </row>
     <row r="460" spans="1:13">
       <c r="A460" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A64, ",", B64, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E460" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E64, ",", F64, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,43);</v>
       </c>
       <c r="I460" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I64, ",", J64, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,43);</v>
       </c>
       <c r="M460" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M64, ",", N64, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,43);</v>
       </c>
     </row>
     <row r="461" spans="1:13">
       <c r="A461" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A65, ",", B65, ");")</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E461" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E65, ",", F65, ");")</f>
+        <f t="shared" si="1"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,44);</v>
       </c>
       <c r="I461" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I65, ",", J65, ");")</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,44);</v>
       </c>
       <c r="M461" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M65, ",", N65, ");")</f>
+        <f t="shared" si="3"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,44);</v>
       </c>
     </row>
     <row r="462" spans="1:13">
       <c r="A462" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A66, ",", B66, ");")</f>
+        <f t="shared" ref="A462:A525" si="4">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A66, ",", B66, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E462" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E66, ",", F66, ");")</f>
+        <f t="shared" ref="E462:E525" si="5">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E66, ",", F66, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,45);</v>
       </c>
       <c r="I462" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I66, ",", J66, ");")</f>
+        <f t="shared" ref="I462:I525" si="6">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I66, ",", J66, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,45);</v>
       </c>
       <c r="M462" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M66, ",", N66, ");")</f>
+        <f t="shared" ref="M462:M525" si="7">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M66, ",", N66, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,45);</v>
       </c>
     </row>
     <row r="463" spans="1:13">
       <c r="A463" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A67, ",", B67, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E463" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E67, ",", F67, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,51);</v>
       </c>
       <c r="I463" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I67, ",", J67, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,51);</v>
       </c>
       <c r="M463" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M67, ",", N67, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,51);</v>
       </c>
     </row>
     <row r="464" spans="1:13">
       <c r="A464" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A68, ",", B68, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E464" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E68, ",", F68, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,56);</v>
       </c>
       <c r="I464" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I68, ",", J68, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,56);</v>
       </c>
       <c r="M464" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M68, ",", N68, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,56);</v>
       </c>
     </row>
     <row r="465" spans="1:13">
       <c r="A465" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A69, ",", B69, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E465" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E69, ",", F69, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,58);</v>
       </c>
       <c r="I465" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I69, ",", J69, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,58);</v>
       </c>
       <c r="M465" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M69, ",", N69, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,58);</v>
       </c>
     </row>
     <row r="466" spans="1:13">
       <c r="A466" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A70, ",", B70, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E466" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E70, ",", F70, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,13);</v>
       </c>
       <c r="I466" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I70, ",", J70, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,13);</v>
       </c>
       <c r="M466" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M70, ",", N70, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,13);</v>
       </c>
     </row>
     <row r="467" spans="1:13">
       <c r="A467" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A71, ",", B71, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E467" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E71, ",", F71, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (6,46);</v>
       </c>
       <c r="I467" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I71, ",", J71, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (7,46);</v>
       </c>
       <c r="M467" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M71, ",", N71, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (8,46);</v>
       </c>
     </row>
     <row r="468" spans="1:13">
       <c r="A468" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A72, ",", B72, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E468" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E72, ",", F72, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I468" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I72, ",", J72, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M468" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M72, ",", N72, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="469" spans="1:13">
       <c r="A469" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A73, ",", B73, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (HAS_PRIVATE_WEB_RESOURCES,);</v>
       </c>
       <c r="E469" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E73, ",", F73, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I469" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I73, ",", J73, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M469" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M73, ",", N73, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="470" spans="1:13">
       <c r="A470" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A74, ",", B74, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,12);</v>
       </c>
       <c r="E470" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E74, ",", F74, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,12);</v>
       </c>
       <c r="I470" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I74, ",", J74, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,12);</v>
       </c>
       <c r="M470" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M74, ",", N74, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,12);</v>
       </c>
     </row>
     <row r="471" spans="1:13">
       <c r="A471" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A75, ",", B75, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,14);</v>
       </c>
       <c r="E471" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E75, ",", F75, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,14);</v>
       </c>
       <c r="I471" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I75, ",", J75, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,14);</v>
       </c>
       <c r="M471" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M75, ",", N75, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,14);</v>
       </c>
     </row>
     <row r="472" spans="1:13">
       <c r="A472" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A76, ",", B76, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,15);</v>
       </c>
       <c r="E472" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E76, ",", F76, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,15);</v>
       </c>
       <c r="I472" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I76, ",", J76, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,15);</v>
       </c>
       <c r="M472" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M76, ",", N76, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,15);</v>
       </c>
     </row>
     <row r="473" spans="1:13">
       <c r="A473" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A77, ",", B77, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,16);</v>
       </c>
       <c r="E473" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E77, ",", F77, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,16);</v>
       </c>
       <c r="I473" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I77, ",", J77, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,16);</v>
       </c>
       <c r="M473" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M77, ",", N77, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,16);</v>
       </c>
     </row>
     <row r="474" spans="1:13">
       <c r="A474" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A78, ",", B78, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,18);</v>
       </c>
       <c r="E474" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E78, ",", F78, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,18);</v>
       </c>
       <c r="I474" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I78, ",", J78, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,18);</v>
       </c>
       <c r="M474" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M78, ",", N78, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,18);</v>
       </c>
     </row>
     <row r="475" spans="1:13">
       <c r="A475" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A79, ",", B79, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,19);</v>
       </c>
       <c r="E475" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E79, ",", F79, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,19);</v>
       </c>
       <c r="I475" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I79, ",", J79, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,19);</v>
       </c>
       <c r="M475" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M79, ",", N79, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,19);</v>
       </c>
     </row>
     <row r="476" spans="1:13">
       <c r="A476" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A80, ",", B80, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,20);</v>
       </c>
       <c r="E476" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E80, ",", F80, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,20);</v>
       </c>
       <c r="I476" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I80, ",", J80, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,20);</v>
       </c>
       <c r="M476" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M80, ",", N80, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,20);</v>
       </c>
     </row>
     <row r="477" spans="1:13">
       <c r="A477" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A81, ",", B81, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,21);</v>
       </c>
       <c r="E477" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E81, ",", F81, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,21);</v>
       </c>
       <c r="I477" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I81, ",", J81, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,21);</v>
       </c>
       <c r="M477" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M81, ",", N81, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,21);</v>
       </c>
     </row>
     <row r="478" spans="1:13">
       <c r="A478" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A82, ",", B82, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,22);</v>
       </c>
       <c r="E478" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E82, ",", F82, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,22);</v>
       </c>
       <c r="I478" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I82, ",", J82, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,22);</v>
       </c>
       <c r="M478" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M82, ",", N82, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,22);</v>
       </c>
     </row>
     <row r="479" spans="1:13">
       <c r="A479" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A83, ",", B83, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,23);</v>
       </c>
       <c r="E479" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E83, ",", F83, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,23);</v>
       </c>
       <c r="I479" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I83, ",", J83, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,23);</v>
       </c>
       <c r="M479" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M83, ",", N83, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,23);</v>
       </c>
     </row>
     <row r="480" spans="1:13">
       <c r="A480" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A84, ",", B84, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,24);</v>
       </c>
       <c r="E480" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E84, ",", F84, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,24);</v>
       </c>
       <c r="I480" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I84, ",", J84, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,24);</v>
       </c>
       <c r="M480" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M84, ",", N84, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,24);</v>
       </c>
     </row>
     <row r="481" spans="1:13">
       <c r="A481" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A85, ",", B85, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,25);</v>
       </c>
       <c r="E481" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E85, ",", F85, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,25);</v>
       </c>
       <c r="I481" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I85, ",", J85, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,25);</v>
       </c>
       <c r="M481" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M85, ",", N85, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,25);</v>
       </c>
     </row>
     <row r="482" spans="1:13">
       <c r="A482" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A86, ",", B86, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,26);</v>
       </c>
       <c r="E482" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E86, ",", F86, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,26);</v>
       </c>
       <c r="I482" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I86, ",", J86, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,26);</v>
       </c>
       <c r="M482" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M86, ",", N86, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,26);</v>
       </c>
     </row>
     <row r="483" spans="1:13">
       <c r="A483" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A87, ",", B87, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,27);</v>
       </c>
       <c r="E483" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E87, ",", F87, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,27);</v>
       </c>
       <c r="I483" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I87, ",", J87, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,27);</v>
       </c>
       <c r="M483" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M87, ",", N87, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,27);</v>
       </c>
     </row>
     <row r="484" spans="1:13">
       <c r="A484" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A88, ",", B88, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,28);</v>
       </c>
       <c r="E484" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E88, ",", F88, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,28);</v>
       </c>
       <c r="I484" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I88, ",", J88, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,28);</v>
       </c>
       <c r="M484" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M88, ",", N88, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,28);</v>
       </c>
     </row>
     <row r="485" spans="1:13">
       <c r="A485" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A89, ",", B89, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,29);</v>
       </c>
       <c r="E485" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E89, ",", F89, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,29);</v>
       </c>
       <c r="I485" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I89, ",", J89, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,29);</v>
       </c>
       <c r="M485" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M89, ",", N89, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,29);</v>
       </c>
     </row>
     <row r="486" spans="1:13">
       <c r="A486" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A90, ",", B90, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,30);</v>
       </c>
       <c r="E486" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E90, ",", F90, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,30);</v>
       </c>
       <c r="I486" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I90, ",", J90, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,30);</v>
       </c>
       <c r="M486" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M90, ",", N90, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,30);</v>
       </c>
     </row>
     <row r="487" spans="1:13">
       <c r="A487" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A91, ",", B91, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,31);</v>
       </c>
       <c r="E487" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E91, ",", F91, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,31);</v>
       </c>
       <c r="I487" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I91, ",", J91, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,31);</v>
       </c>
       <c r="M487" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M91, ",", N91, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,31);</v>
       </c>
     </row>
     <row r="488" spans="1:13">
       <c r="A488" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A92, ",", B92, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,32);</v>
       </c>
       <c r="E488" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E92, ",", F92, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,32);</v>
       </c>
       <c r="I488" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I92, ",", J92, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,32);</v>
       </c>
       <c r="M488" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M92, ",", N92, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,32);</v>
       </c>
     </row>
     <row r="489" spans="1:13">
       <c r="A489" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A93, ",", B93, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,35);</v>
       </c>
       <c r="E489" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E93, ",", F93, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,35);</v>
       </c>
       <c r="I489" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I93, ",", J93, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,35);</v>
       </c>
       <c r="M489" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M93, ",", N93, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,35);</v>
       </c>
     </row>
     <row r="490" spans="1:13">
       <c r="A490" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A94, ",", B94, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,36);</v>
       </c>
       <c r="E490" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E94, ",", F94, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,36);</v>
       </c>
       <c r="I490" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I94, ",", J94, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,36);</v>
       </c>
       <c r="M490" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M94, ",", N94, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,36);</v>
       </c>
     </row>
     <row r="491" spans="1:13">
       <c r="A491" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A95, ",", B95, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,59);</v>
       </c>
       <c r="E491" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E95, ",", F95, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,59);</v>
       </c>
       <c r="I491" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I95, ",", J95, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,59);</v>
       </c>
       <c r="M491" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M95, ",", N95, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,59);</v>
       </c>
     </row>
     <row r="492" spans="1:13">
       <c r="A492" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A96, ",", B96, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,60);</v>
       </c>
       <c r="E492" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E96, ",", F96, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,60);</v>
       </c>
       <c r="I492" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I96, ",", J96, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,60);</v>
       </c>
       <c r="M492" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M96, ",", N96, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,60);</v>
       </c>
     </row>
     <row r="493" spans="1:13">
       <c r="A493" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A97, ",", B97, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,63);</v>
       </c>
       <c r="E493" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E97, ",", F97, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,63);</v>
       </c>
       <c r="I493" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I97, ",", J97, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,63);</v>
       </c>
       <c r="M493" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M97, ",", N97, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,63);</v>
       </c>
     </row>
     <row r="494" spans="1:13">
       <c r="A494" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A98, ",", B98, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,65);</v>
       </c>
       <c r="E494" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E98, ",", F98, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,65);</v>
       </c>
       <c r="I494" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I98, ",", J98, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,65);</v>
       </c>
       <c r="M494" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M98, ",", N98, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,65);</v>
       </c>
     </row>
     <row r="495" spans="1:13">
       <c r="A495" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A99, ",", B99, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (9,34);</v>
       </c>
       <c r="E495" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E99, ",", F99, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,37);</v>
       </c>
       <c r="I495" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I99, ",", J99, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,37);</v>
       </c>
       <c r="M495" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M99, ",", N99, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,37);</v>
       </c>
     </row>
     <row r="496" spans="1:13">
       <c r="A496" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A100, ",", B100, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E496" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E100, ",", F100, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,38);</v>
       </c>
       <c r="I496" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I100, ",", J100, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,38);</v>
       </c>
       <c r="M496" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M100, ",", N100, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,38);</v>
       </c>
     </row>
     <row r="497" spans="1:13">
       <c r="A497" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A101, ",", B101, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E497" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E101, ",", F101, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,43);</v>
       </c>
       <c r="I497" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I101, ",", J101, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,43);</v>
       </c>
       <c r="M497" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M101, ",", N101, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,43);</v>
       </c>
     </row>
     <row r="498" spans="1:13">
       <c r="A498" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A102, ",", B102, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E498" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E102, ",", F102, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,44);</v>
       </c>
       <c r="I498" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I102, ",", J102, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,44);</v>
       </c>
       <c r="M498" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M102, ",", N102, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,44);</v>
       </c>
     </row>
     <row r="499" spans="1:13">
       <c r="A499" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A103, ",", B103, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E499" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E103, ",", F103, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,45);</v>
       </c>
       <c r="I499" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I103, ",", J103, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,45);</v>
       </c>
       <c r="M499" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M103, ",", N103, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,45);</v>
       </c>
     </row>
     <row r="500" spans="1:13">
       <c r="A500" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A104, ",", B104, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E500" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E104, ",", F104, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,51);</v>
       </c>
       <c r="I500" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I104, ",", J104, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,51);</v>
       </c>
       <c r="M500" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M104, ",", N104, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,51);</v>
       </c>
     </row>
     <row r="501" spans="1:13">
       <c r="A501" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A105, ",", B105, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E501" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E105, ",", F105, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,56);</v>
       </c>
       <c r="I501" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I105, ",", J105, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,56);</v>
       </c>
       <c r="M501" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M105, ",", N105, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,56);</v>
       </c>
     </row>
     <row r="502" spans="1:13">
       <c r="A502" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A106, ",", B106, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E502" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E106, ",", F106, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,58);</v>
       </c>
       <c r="I502" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I106, ",", J106, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,58);</v>
       </c>
       <c r="M502" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M106, ",", N106, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,58);</v>
       </c>
     </row>
     <row r="503" spans="1:13">
       <c r="A503" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A107, ",", B107, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E503" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E107, ",", F107, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (10,34);</v>
       </c>
       <c r="I503" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I107, ",", J107, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (11,34);</v>
       </c>
       <c r="M503" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M107, ",", N107, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (12,34);</v>
       </c>
     </row>
     <row r="504" spans="1:13">
       <c r="A504" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A108, ",", B108, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (HAS_PUBLIC_WEB_RESOURCES,);</v>
       </c>
       <c r="E504" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E108, ",", F108, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I504" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I108, ",", J108, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M504" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M108, ",", N108, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="505" spans="1:13">
       <c r="A505" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A109, ",", B109, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,12);</v>
       </c>
       <c r="E505" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E109, ",", F109, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,12);</v>
       </c>
       <c r="I505" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I109, ",", J109, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,12);</v>
       </c>
       <c r="M505" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M109, ",", N109, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,12);</v>
       </c>
     </row>
     <row r="506" spans="1:13">
       <c r="A506" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A110, ",", B110, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,14);</v>
       </c>
       <c r="E506" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E110, ",", F110, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,14);</v>
       </c>
       <c r="I506" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I110, ",", J110, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,14);</v>
       </c>
       <c r="M506" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M110, ",", N110, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,14);</v>
       </c>
     </row>
     <row r="507" spans="1:13">
       <c r="A507" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A111, ",", B111, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,15);</v>
       </c>
       <c r="E507" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E111, ",", F111, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,15);</v>
       </c>
       <c r="I507" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I111, ",", J111, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,15);</v>
       </c>
       <c r="M507" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M111, ",", N111, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,15);</v>
       </c>
     </row>
     <row r="508" spans="1:13">
       <c r="A508" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A112, ",", B112, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,16);</v>
       </c>
       <c r="E508" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E112, ",", F112, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,16);</v>
       </c>
       <c r="I508" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I112, ",", J112, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,16);</v>
       </c>
       <c r="M508" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M112, ",", N112, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,16);</v>
       </c>
     </row>
     <row r="509" spans="1:13">
       <c r="A509" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A113, ",", B113, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,18);</v>
       </c>
       <c r="E509" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E113, ",", F113, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,18);</v>
       </c>
       <c r="I509" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I113, ",", J113, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,18);</v>
       </c>
       <c r="M509" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M113, ",", N113, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,18);</v>
       </c>
     </row>
     <row r="510" spans="1:13">
       <c r="A510" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A114, ",", B114, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,19);</v>
       </c>
       <c r="E510" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E114, ",", F114, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,19);</v>
       </c>
       <c r="I510" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I114, ",", J114, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,19);</v>
       </c>
       <c r="M510" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M114, ",", N114, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,19);</v>
       </c>
     </row>
     <row r="511" spans="1:13">
       <c r="A511" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A115, ",", B115, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,20);</v>
       </c>
       <c r="E511" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E115, ",", F115, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,20);</v>
       </c>
       <c r="I511" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I115, ",", J115, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,20);</v>
       </c>
       <c r="M511" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M115, ",", N115, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,20);</v>
       </c>
     </row>
     <row r="512" spans="1:13">
       <c r="A512" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A116, ",", B116, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,21);</v>
       </c>
       <c r="E512" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E116, ",", F116, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,21);</v>
       </c>
       <c r="I512" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I116, ",", J116, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,21);</v>
       </c>
       <c r="M512" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M116, ",", N116, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,21);</v>
       </c>
     </row>
     <row r="513" spans="1:13">
       <c r="A513" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A117, ",", B117, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,22);</v>
       </c>
       <c r="E513" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E117, ",", F117, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,22);</v>
       </c>
       <c r="I513" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I117, ",", J117, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,22);</v>
       </c>
       <c r="M513" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M117, ",", N117, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,22);</v>
       </c>
     </row>
     <row r="514" spans="1:13">
       <c r="A514" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A118, ",", B118, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,23);</v>
       </c>
       <c r="E514" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E118, ",", F118, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,23);</v>
       </c>
       <c r="I514" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I118, ",", J118, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,23);</v>
       </c>
       <c r="M514" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M118, ",", N118, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,23);</v>
       </c>
     </row>
     <row r="515" spans="1:13">
       <c r="A515" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A119, ",", B119, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,24);</v>
       </c>
       <c r="E515" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E119, ",", F119, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,24);</v>
       </c>
       <c r="I515" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I119, ",", J119, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,24);</v>
       </c>
       <c r="M515" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M119, ",", N119, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,24);</v>
       </c>
     </row>
     <row r="516" spans="1:13">
       <c r="A516" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A120, ",", B120, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,25);</v>
       </c>
       <c r="E516" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E120, ",", F120, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,25);</v>
       </c>
       <c r="I516" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I120, ",", J120, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,25);</v>
       </c>
       <c r="M516" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M120, ",", N120, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,25);</v>
       </c>
     </row>
     <row r="517" spans="1:13">
       <c r="A517" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A121, ",", B121, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,26);</v>
       </c>
       <c r="E517" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E121, ",", F121, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,26);</v>
       </c>
       <c r="I517" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I121, ",", J121, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,26);</v>
       </c>
       <c r="M517" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M121, ",", N121, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,26);</v>
       </c>
     </row>
     <row r="518" spans="1:13">
       <c r="A518" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A122, ",", B122, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,27);</v>
       </c>
       <c r="E518" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E122, ",", F122, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,27);</v>
       </c>
       <c r="I518" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I122, ",", J122, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,27);</v>
       </c>
       <c r="M518" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M122, ",", N122, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,27);</v>
       </c>
     </row>
     <row r="519" spans="1:13">
       <c r="A519" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A123, ",", B123, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,28);</v>
       </c>
       <c r="E519" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E123, ",", F123, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,28);</v>
       </c>
       <c r="I519" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I123, ",", J123, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,28);</v>
       </c>
       <c r="M519" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M123, ",", N123, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,28);</v>
       </c>
     </row>
     <row r="520" spans="1:13">
       <c r="A520" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A124, ",", B124, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,29);</v>
       </c>
       <c r="E520" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E124, ",", F124, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,29);</v>
       </c>
       <c r="I520" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I124, ",", J124, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,29);</v>
       </c>
       <c r="M520" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M124, ",", N124, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,29);</v>
       </c>
     </row>
     <row r="521" spans="1:13">
       <c r="A521" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A125, ",", B125, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,30);</v>
       </c>
       <c r="E521" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E125, ",", F125, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,30);</v>
       </c>
       <c r="I521" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I125, ",", J125, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,30);</v>
       </c>
       <c r="M521" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M125, ",", N125, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,30);</v>
       </c>
     </row>
     <row r="522" spans="1:13">
       <c r="A522" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A126, ",", B126, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,31);</v>
       </c>
       <c r="E522" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E126, ",", F126, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,31);</v>
       </c>
       <c r="I522" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I126, ",", J126, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,31);</v>
       </c>
       <c r="M522" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M126, ",", N126, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,31);</v>
       </c>
     </row>
     <row r="523" spans="1:13">
       <c r="A523" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A127, ",", B127, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,32);</v>
       </c>
       <c r="E523" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E127, ",", F127, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,32);</v>
       </c>
       <c r="I523" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I127, ",", J127, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,32);</v>
       </c>
       <c r="M523" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M127, ",", N127, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,32);</v>
       </c>
     </row>
     <row r="524" spans="1:13">
       <c r="A524" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A128, ",", B128, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,35);</v>
       </c>
       <c r="E524" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E128, ",", F128, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,35);</v>
       </c>
       <c r="I524" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I128, ",", J128, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,35);</v>
       </c>
       <c r="M524" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M128, ",", N128, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,35);</v>
       </c>
     </row>
     <row r="525" spans="1:13">
       <c r="A525" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A129, ",", B129, ");")</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,36);</v>
       </c>
       <c r="E525" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E129, ",", F129, ");")</f>
+        <f t="shared" si="5"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,36);</v>
       </c>
       <c r="I525" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I129, ",", J129, ");")</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,36);</v>
       </c>
       <c r="M525" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M129, ",", N129, ");")</f>
+        <f t="shared" si="7"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,36);</v>
       </c>
     </row>
     <row r="526" spans="1:13">
       <c r="A526" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A130, ",", B130, ");")</f>
+        <f t="shared" ref="A526:A589" si="8">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A130, ",", B130, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,59);</v>
       </c>
       <c r="E526" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E130, ",", F130, ");")</f>
+        <f t="shared" ref="E526:E589" si="9">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E130, ",", F130, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,59);</v>
       </c>
       <c r="I526" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I130, ",", J130, ");")</f>
+        <f t="shared" ref="I526:I589" si="10">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I130, ",", J130, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,59);</v>
       </c>
       <c r="M526" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M130, ",", N130, ");")</f>
+        <f t="shared" ref="M526:M589" si="11">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M130, ",", N130, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,59);</v>
       </c>
     </row>
     <row r="527" spans="1:13">
       <c r="A527" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A131, ",", B131, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,60);</v>
       </c>
       <c r="E527" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E131, ",", F131, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,60);</v>
       </c>
       <c r="I527" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I131, ",", J131, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,60);</v>
       </c>
       <c r="M527" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M131, ",", N131, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,60);</v>
       </c>
     </row>
     <row r="528" spans="1:13">
       <c r="A528" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A132, ",", B132, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,63);</v>
       </c>
       <c r="E528" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E132, ",", F132, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,63);</v>
       </c>
       <c r="I528" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I132, ",", J132, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,63);</v>
       </c>
       <c r="M528" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M132, ",", N132, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,63);</v>
       </c>
     </row>
     <row r="529" spans="1:13">
       <c r="A529" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A133, ",", B133, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,65);</v>
       </c>
       <c r="E529" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E133, ",", F133, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,65);</v>
       </c>
       <c r="I529" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I133, ",", J133, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,65);</v>
       </c>
       <c r="M529" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M133, ",", N133, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,65);</v>
       </c>
     </row>
     <row r="530" spans="1:13">
       <c r="A530" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A134, ",", B134, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,33);</v>
       </c>
       <c r="E530" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E134, ",", F134, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,37);</v>
       </c>
       <c r="I530" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I134, ",", J134, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,37);</v>
       </c>
       <c r="M530" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M134, ",", N134, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,37);</v>
       </c>
     </row>
     <row r="531" spans="1:13">
       <c r="A531" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A135, ",", B135, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (13,34);</v>
       </c>
       <c r="E531" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E135, ",", F135, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,38);</v>
       </c>
       <c r="I531" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I135, ",", J135, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,38);</v>
       </c>
       <c r="M531" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M135, ",", N135, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,38);</v>
       </c>
     </row>
     <row r="532" spans="1:13">
       <c r="A532" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A136, ",", B136, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E532" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E136, ",", F136, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,43);</v>
       </c>
       <c r="I532" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I136, ",", J136, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,43);</v>
       </c>
       <c r="M532" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M136, ",", N136, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,43);</v>
       </c>
     </row>
     <row r="533" spans="1:13">
       <c r="A533" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A137, ",", B137, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E533" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E137, ",", F137, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,44);</v>
       </c>
       <c r="I533" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I137, ",", J137, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,44);</v>
       </c>
       <c r="M533" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M137, ",", N137, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,44);</v>
       </c>
     </row>
     <row r="534" spans="1:13">
       <c r="A534" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A138, ",", B138, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E534" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E138, ",", F138, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,45);</v>
       </c>
       <c r="I534" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I138, ",", J138, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,45);</v>
       </c>
       <c r="M534" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M138, ",", N138, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,45);</v>
       </c>
     </row>
     <row r="535" spans="1:13">
       <c r="A535" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A139, ",", B139, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E535" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E139, ",", F139, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,51);</v>
       </c>
       <c r="I535" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I139, ",", J139, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,51);</v>
       </c>
       <c r="M535" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M139, ",", N139, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,51);</v>
       </c>
     </row>
     <row r="536" spans="1:13">
       <c r="A536" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A140, ",", B140, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E536" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E140, ",", F140, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,56);</v>
       </c>
       <c r="I536" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I140, ",", J140, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,56);</v>
       </c>
       <c r="M536" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M140, ",", N140, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,56);</v>
       </c>
     </row>
     <row r="537" spans="1:13">
       <c r="A537" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A141, ",", B141, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E537" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E141, ",", F141, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,58);</v>
       </c>
       <c r="I537" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I141, ",", J141, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,58);</v>
       </c>
       <c r="M537" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M141, ",", N141, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,58);</v>
       </c>
     </row>
     <row r="538" spans="1:13">
       <c r="A538" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A142, ",", B142, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E538" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E142, ",", F142, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,33);</v>
       </c>
       <c r="I538" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I142, ",", J142, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,33);</v>
       </c>
       <c r="M538" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M142, ",", N142, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,33);</v>
       </c>
     </row>
     <row r="539" spans="1:13">
       <c r="A539" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A143, ",", B143, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E539" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E143, ",", F143, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (14,34);</v>
       </c>
       <c r="I539" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I143, ",", J143, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (15,34);</v>
       </c>
       <c r="M539" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M143, ",", N143, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (16,34);</v>
       </c>
     </row>
     <row r="540" spans="1:13">
       <c r="A540" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A144, ",", B144, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E540" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E144, ",", F144, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I540" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I144, ",", J144, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M540" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M144, ",", N144, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="541" spans="1:13">
       <c r="A541" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A145, ",", B145, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (TRANSPORTATION,);</v>
       </c>
       <c r="E541" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E145, ",", F145, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I541" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I145, ",", J145, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M541" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M145, ",", N145, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="542" spans="1:13">
       <c r="A542" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A146, ",", B146, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,12);</v>
       </c>
       <c r="E542" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E146, ",", F146, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,12);</v>
       </c>
       <c r="I542" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I146, ",", J146, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,12);</v>
       </c>
       <c r="M542" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M146, ",", N146, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,12);</v>
       </c>
     </row>
     <row r="543" spans="1:13">
       <c r="A543" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A147, ",", B147, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,14);</v>
       </c>
       <c r="E543" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E147, ",", F147, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,14);</v>
       </c>
       <c r="I543" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I147, ",", J147, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,14);</v>
       </c>
       <c r="M543" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M147, ",", N147, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,14);</v>
       </c>
     </row>
     <row r="544" spans="1:13">
       <c r="A544" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A148, ",", B148, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,15);</v>
       </c>
       <c r="E544" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E148, ",", F148, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,15);</v>
       </c>
       <c r="I544" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I148, ",", J148, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,15);</v>
       </c>
       <c r="M544" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M148, ",", N148, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,15);</v>
       </c>
     </row>
     <row r="545" spans="1:13">
       <c r="A545" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A149, ",", B149, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,16);</v>
       </c>
       <c r="E545" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E149, ",", F149, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,16);</v>
       </c>
       <c r="I545" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I149, ",", J149, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,16);</v>
       </c>
       <c r="M545" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M149, ",", N149, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,16);</v>
       </c>
     </row>
     <row r="546" spans="1:13">
       <c r="A546" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A150, ",", B150, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,18);</v>
       </c>
       <c r="E546" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E150, ",", F150, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,18);</v>
       </c>
       <c r="I546" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I150, ",", J150, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,18);</v>
       </c>
       <c r="M546" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M150, ",", N150, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,18);</v>
       </c>
     </row>
     <row r="547" spans="1:13">
       <c r="A547" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A151, ",", B151, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,19);</v>
       </c>
       <c r="E547" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E151, ",", F151, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,19);</v>
       </c>
       <c r="I547" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I151, ",", J151, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,19);</v>
       </c>
       <c r="M547" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M151, ",", N151, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,19);</v>
       </c>
     </row>
     <row r="548" spans="1:13">
       <c r="A548" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A152, ",", B152, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,20);</v>
       </c>
       <c r="E548" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E152, ",", F152, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,20);</v>
       </c>
       <c r="I548" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I152, ",", J152, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,20);</v>
       </c>
       <c r="M548" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M152, ",", N152, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,20);</v>
       </c>
     </row>
     <row r="549" spans="1:13">
       <c r="A549" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A153, ",", B153, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,21);</v>
       </c>
       <c r="E549" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E153, ",", F153, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,21);</v>
       </c>
       <c r="I549" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I153, ",", J153, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,21);</v>
       </c>
       <c r="M549" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M153, ",", N153, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,21);</v>
       </c>
     </row>
     <row r="550" spans="1:13">
       <c r="A550" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A154, ",", B154, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,22);</v>
       </c>
       <c r="E550" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E154, ",", F154, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,22);</v>
       </c>
       <c r="I550" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I154, ",", J154, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,22);</v>
       </c>
       <c r="M550" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M154, ",", N154, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,22);</v>
       </c>
     </row>
     <row r="551" spans="1:13">
       <c r="A551" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A155, ",", B155, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,23);</v>
       </c>
       <c r="E551" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E155, ",", F155, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,23);</v>
       </c>
       <c r="I551" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I155, ",", J155, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,23);</v>
       </c>
       <c r="M551" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M155, ",", N155, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,23);</v>
       </c>
     </row>
     <row r="552" spans="1:13">
       <c r="A552" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A156, ",", B156, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,24);</v>
       </c>
       <c r="E552" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E156, ",", F156, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,24);</v>
       </c>
       <c r="I552" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I156, ",", J156, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,24);</v>
       </c>
       <c r="M552" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M156, ",", N156, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,24);</v>
       </c>
     </row>
     <row r="553" spans="1:13">
       <c r="A553" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A157, ",", B157, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,25);</v>
       </c>
       <c r="E553" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E157, ",", F157, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,25);</v>
       </c>
       <c r="I553" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I157, ",", J157, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,25);</v>
       </c>
       <c r="M553" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M157, ",", N157, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,25);</v>
       </c>
     </row>
     <row r="554" spans="1:13">
       <c r="A554" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A158, ",", B158, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,26);</v>
       </c>
       <c r="E554" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E158, ",", F158, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,26);</v>
       </c>
       <c r="I554" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I158, ",", J158, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,26);</v>
       </c>
       <c r="M554" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M158, ",", N158, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,26);</v>
       </c>
     </row>
     <row r="555" spans="1:13">
       <c r="A555" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A159, ",", B159, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,27);</v>
       </c>
       <c r="E555" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E159, ",", F159, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,27);</v>
       </c>
       <c r="I555" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I159, ",", J159, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,27);</v>
       </c>
       <c r="M555" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M159, ",", N159, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,27);</v>
       </c>
     </row>
     <row r="556" spans="1:13">
       <c r="A556" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A160, ",", B160, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,28);</v>
       </c>
       <c r="E556" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E160, ",", F160, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,28);</v>
       </c>
       <c r="I556" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I160, ",", J160, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,28);</v>
       </c>
       <c r="M556" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M160, ",", N160, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,28);</v>
       </c>
     </row>
     <row r="557" spans="1:13">
       <c r="A557" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A161, ",", B161, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,29);</v>
       </c>
       <c r="E557" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E161, ",", F161, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,29);</v>
       </c>
       <c r="I557" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I161, ",", J161, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,29);</v>
       </c>
       <c r="M557" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M161, ",", N161, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,29);</v>
       </c>
     </row>
     <row r="558" spans="1:13">
       <c r="A558" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A162, ",", B162, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,30);</v>
       </c>
       <c r="E558" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E162, ",", F162, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,30);</v>
       </c>
       <c r="I558" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I162, ",", J162, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,30);</v>
       </c>
       <c r="M558" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M162, ",", N162, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,30);</v>
       </c>
     </row>
     <row r="559" spans="1:13">
       <c r="A559" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A163, ",", B163, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,31);</v>
       </c>
       <c r="E559" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E163, ",", F163, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,31);</v>
       </c>
       <c r="I559" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I163, ",", J163, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,31);</v>
       </c>
       <c r="M559" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M163, ",", N163, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,31);</v>
       </c>
     </row>
     <row r="560" spans="1:13">
       <c r="A560" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A164, ",", B164, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,32);</v>
       </c>
       <c r="E560" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E164, ",", F164, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,32);</v>
       </c>
       <c r="I560" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I164, ",", J164, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,32);</v>
       </c>
       <c r="M560" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M164, ",", N164, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,32);</v>
       </c>
     </row>
     <row r="561" spans="1:13">
       <c r="A561" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A165, ",", B165, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,35);</v>
       </c>
       <c r="E561" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E165, ",", F165, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,35);</v>
       </c>
       <c r="I561" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I165, ",", J165, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,35);</v>
       </c>
       <c r="M561" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M165, ",", N165, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,35);</v>
       </c>
     </row>
     <row r="562" spans="1:13">
       <c r="A562" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A166, ",", B166, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,36);</v>
       </c>
       <c r="E562" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E166, ",", F166, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,36);</v>
       </c>
       <c r="I562" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I166, ",", J166, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,36);</v>
       </c>
       <c r="M562" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M166, ",", N166, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,36);</v>
       </c>
     </row>
     <row r="563" spans="1:13">
       <c r="A563" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A167, ",", B167, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,59);</v>
       </c>
       <c r="E563" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E167, ",", F167, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,59);</v>
       </c>
       <c r="I563" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I167, ",", J167, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,59);</v>
       </c>
       <c r="M563" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M167, ",", N167, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,59);</v>
       </c>
     </row>
     <row r="564" spans="1:13">
       <c r="A564" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A168, ",", B168, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,60);</v>
       </c>
       <c r="E564" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E168, ",", F168, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,60);</v>
       </c>
       <c r="I564" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I168, ",", J168, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,60);</v>
       </c>
       <c r="M564" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M168, ",", N168, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,60);</v>
       </c>
     </row>
     <row r="565" spans="1:13">
       <c r="A565" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A169, ",", B169, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,63);</v>
       </c>
       <c r="E565" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E169, ",", F169, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,63);</v>
       </c>
       <c r="I565" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I169, ",", J169, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,63);</v>
       </c>
       <c r="M565" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M169, ",", N169, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,63);</v>
       </c>
     </row>
     <row r="566" spans="1:13">
       <c r="A566" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A170, ",", B170, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (17,65);</v>
       </c>
       <c r="E566" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E170, ",", F170, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,65);</v>
       </c>
       <c r="I566" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I170, ",", J170, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,65);</v>
       </c>
       <c r="M566" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M170, ",", N170, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,65);</v>
       </c>
     </row>
     <row r="567" spans="1:13">
       <c r="A567" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A171, ",", B171, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E567" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E171, ",", F171, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,37);</v>
       </c>
       <c r="I567" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I171, ",", J171, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,37);</v>
       </c>
       <c r="M567" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M171, ",", N171, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,37);</v>
       </c>
     </row>
     <row r="568" spans="1:13">
       <c r="A568" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A172, ",", B172, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E568" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E172, ",", F172, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,38);</v>
       </c>
       <c r="I568" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I172, ",", J172, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,38);</v>
       </c>
       <c r="M568" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M172, ",", N172, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,38);</v>
       </c>
     </row>
     <row r="569" spans="1:13">
       <c r="A569" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A173, ",", B173, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E569" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E173, ",", F173, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,43);</v>
       </c>
       <c r="I569" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I173, ",", J173, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,43);</v>
       </c>
       <c r="M569" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M173, ",", N173, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,43);</v>
       </c>
     </row>
     <row r="570" spans="1:13">
       <c r="A570" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A174, ",", B174, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E570" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E174, ",", F174, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,44);</v>
       </c>
       <c r="I570" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I174, ",", J174, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,44);</v>
       </c>
       <c r="M570" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M174, ",", N174, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,44);</v>
       </c>
     </row>
     <row r="571" spans="1:13">
       <c r="A571" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A175, ",", B175, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E571" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E175, ",", F175, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,45);</v>
       </c>
       <c r="I571" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I175, ",", J175, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,45);</v>
       </c>
       <c r="M571" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M175, ",", N175, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,45);</v>
       </c>
     </row>
     <row r="572" spans="1:13">
       <c r="A572" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A176, ",", B176, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E572" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E176, ",", F176, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,51);</v>
       </c>
       <c r="I572" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I176, ",", J176, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,51);</v>
       </c>
       <c r="M572" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M176, ",", N176, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,51);</v>
       </c>
     </row>
     <row r="573" spans="1:13">
       <c r="A573" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A177, ",", B177, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E573" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E177, ",", F177, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,56);</v>
       </c>
       <c r="I573" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I177, ",", J177, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,56);</v>
       </c>
       <c r="M573" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M177, ",", N177, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,56);</v>
       </c>
     </row>
     <row r="574" spans="1:13">
       <c r="A574" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A178, ",", B178, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E574" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E178, ",", F178, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,58);</v>
       </c>
       <c r="I574" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I178, ",", J178, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,58);</v>
       </c>
       <c r="M574" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M178, ",", N178, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,58);</v>
       </c>
     </row>
     <row r="575" spans="1:13">
       <c r="A575" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A179, ",", B179, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E575" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E179, ",", F179, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (18,39);</v>
       </c>
       <c r="I575" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I179, ",", J179, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (19,39);</v>
       </c>
       <c r="M575" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M179, ",", N179, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (20,39);</v>
       </c>
     </row>
     <row r="576" spans="1:13">
       <c r="A576" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A180, ",", B180, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (GOVERNMENT,);</v>
       </c>
       <c r="E576" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E180, ",", F180, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I576" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I180, ",", J180, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M576" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M180, ",", N180, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="577" spans="1:13">
       <c r="A577" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A181, ",", B181, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,12);</v>
       </c>
       <c r="E577" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E181, ",", F181, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,12);</v>
       </c>
       <c r="I577" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I181, ",", J181, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,12);</v>
       </c>
       <c r="M577" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M181, ",", N181, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,12);</v>
       </c>
     </row>
     <row r="578" spans="1:13">
       <c r="A578" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A182, ",", B182, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,14);</v>
       </c>
       <c r="E578" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E182, ",", F182, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,14);</v>
       </c>
       <c r="I578" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I182, ",", J182, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,14);</v>
       </c>
       <c r="M578" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M182, ",", N182, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,14);</v>
       </c>
     </row>
     <row r="579" spans="1:13">
       <c r="A579" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A183, ",", B183, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,15);</v>
       </c>
       <c r="E579" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E183, ",", F183, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,15);</v>
       </c>
       <c r="I579" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I183, ",", J183, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,15);</v>
       </c>
       <c r="M579" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M183, ",", N183, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,15);</v>
       </c>
     </row>
     <row r="580" spans="1:13">
       <c r="A580" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A184, ",", B184, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,16);</v>
       </c>
       <c r="E580" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E184, ",", F184, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,16);</v>
       </c>
       <c r="I580" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I184, ",", J184, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,16);</v>
       </c>
       <c r="M580" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M184, ",", N184, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,16);</v>
       </c>
     </row>
     <row r="581" spans="1:13">
       <c r="A581" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A185, ",", B185, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,18);</v>
       </c>
       <c r="E581" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E185, ",", F185, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,18);</v>
       </c>
       <c r="I581" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I185, ",", J185, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,18);</v>
       </c>
       <c r="M581" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M185, ",", N185, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,18);</v>
       </c>
     </row>
     <row r="582" spans="1:13">
       <c r="A582" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A186, ",", B186, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,19);</v>
       </c>
       <c r="E582" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E186, ",", F186, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,19);</v>
       </c>
       <c r="I582" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I186, ",", J186, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,19);</v>
       </c>
       <c r="M582" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M186, ",", N186, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,19);</v>
       </c>
     </row>
     <row r="583" spans="1:13">
       <c r="A583" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A187, ",", B187, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,22);</v>
       </c>
       <c r="E583" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E187, ",", F187, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,22);</v>
       </c>
       <c r="I583" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I187, ",", J187, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,22);</v>
       </c>
       <c r="M583" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M187, ",", N187, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,22);</v>
       </c>
     </row>
     <row r="584" spans="1:13">
       <c r="A584" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A188, ",", B188, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,24);</v>
       </c>
       <c r="E584" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E188, ",", F188, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,24);</v>
       </c>
       <c r="I584" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I188, ",", J188, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,24);</v>
       </c>
       <c r="M584" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M188, ",", N188, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,24);</v>
       </c>
     </row>
     <row r="585" spans="1:13">
       <c r="A585" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A189, ",", B189, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,25);</v>
       </c>
       <c r="E585" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E189, ",", F189, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,25);</v>
       </c>
       <c r="I585" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I189, ",", J189, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,25);</v>
       </c>
       <c r="M585" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M189, ",", N189, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,25);</v>
       </c>
     </row>
     <row r="586" spans="1:13">
       <c r="A586" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A190, ",", B190, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,26);</v>
       </c>
       <c r="E586" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E190, ",", F190, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,26);</v>
       </c>
       <c r="I586" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I190, ",", J190, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,26);</v>
       </c>
       <c r="M586" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M190, ",", N190, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,26);</v>
       </c>
     </row>
     <row r="587" spans="1:13">
       <c r="A587" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A191, ",", B191, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,27);</v>
       </c>
       <c r="E587" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E191, ",", F191, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,27);</v>
       </c>
       <c r="I587" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I191, ",", J191, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,27);</v>
       </c>
       <c r="M587" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M191, ",", N191, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,27);</v>
       </c>
     </row>
     <row r="588" spans="1:13">
       <c r="A588" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A192, ",", B192, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,28);</v>
       </c>
       <c r="E588" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E192, ",", F192, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,28);</v>
       </c>
       <c r="I588" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I192, ",", J192, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,28);</v>
       </c>
       <c r="M588" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M192, ",", N192, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,28);</v>
       </c>
     </row>
     <row r="589" spans="1:13">
       <c r="A589" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A193, ",", B193, ");")</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,29);</v>
       </c>
       <c r="E589" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E193, ",", F193, ");")</f>
+        <f t="shared" si="9"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,29);</v>
       </c>
       <c r="I589" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I193, ",", J193, ");")</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,29);</v>
       </c>
       <c r="M589" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M193, ",", N193, ");")</f>
+        <f t="shared" si="11"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,29);</v>
       </c>
     </row>
     <row r="590" spans="1:13">
       <c r="A590" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A194, ",", B194, ");")</f>
+        <f t="shared" ref="A590:A653" si="12">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A194, ",", B194, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,30);</v>
       </c>
       <c r="E590" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E194, ",", F194, ");")</f>
+        <f t="shared" ref="E590:E653" si="13">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E194, ",", F194, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,30);</v>
       </c>
       <c r="I590" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I194, ",", J194, ");")</f>
+        <f t="shared" ref="I590:I653" si="14">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I194, ",", J194, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,30);</v>
       </c>
       <c r="M590" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M194, ",", N194, ");")</f>
+        <f t="shared" ref="M590:M653" si="15">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M194, ",", N194, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,30);</v>
       </c>
     </row>
     <row r="591" spans="1:13">
       <c r="A591" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A195, ",", B195, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,31);</v>
       </c>
       <c r="E591" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E195, ",", F195, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,31);</v>
       </c>
       <c r="I591" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I195, ",", J195, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,31);</v>
       </c>
       <c r="M591" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M195, ",", N195, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,31);</v>
       </c>
     </row>
     <row r="592" spans="1:13">
       <c r="A592" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A196, ",", B196, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,32);</v>
       </c>
       <c r="E592" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E196, ",", F196, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,32);</v>
       </c>
       <c r="I592" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I196, ",", J196, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,32);</v>
       </c>
       <c r="M592" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M196, ",", N196, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,32);</v>
       </c>
     </row>
     <row r="593" spans="1:13">
       <c r="A593" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A197, ",", B197, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,35);</v>
       </c>
       <c r="E593" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E197, ",", F197, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,35);</v>
       </c>
       <c r="I593" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I197, ",", J197, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,35);</v>
       </c>
       <c r="M593" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M197, ",", N197, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,35);</v>
       </c>
     </row>
     <row r="594" spans="1:13">
       <c r="A594" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A198, ",", B198, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,36);</v>
       </c>
       <c r="E594" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E198, ",", F198, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,36);</v>
       </c>
       <c r="I594" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I198, ",", J198, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,36);</v>
       </c>
       <c r="M594" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M198, ",", N198, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,36);</v>
       </c>
     </row>
     <row r="595" spans="1:13">
       <c r="A595" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A199, ",", B199, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,59);</v>
       </c>
       <c r="E595" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E199, ",", F199, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,59);</v>
       </c>
       <c r="I595" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I199, ",", J199, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,59);</v>
       </c>
       <c r="M595" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M199, ",", N199, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,59);</v>
       </c>
     </row>
     <row r="596" spans="1:13">
       <c r="A596" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A200, ",", B200, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,60);</v>
       </c>
       <c r="E596" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E200, ",", F200, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,60);</v>
       </c>
       <c r="I596" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I200, ",", J200, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,60);</v>
       </c>
       <c r="M596" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M200, ",", N200, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,60);</v>
       </c>
     </row>
     <row r="597" spans="1:13">
       <c r="A597" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A201, ",", B201, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,63);</v>
       </c>
       <c r="E597" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E201, ",", F201, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,63);</v>
       </c>
       <c r="I597" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I201, ",", J201, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,63);</v>
       </c>
       <c r="M597" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M201, ",", N201, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,63);</v>
       </c>
     </row>
     <row r="598" spans="1:13">
       <c r="A598" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A202, ",", B202, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,65);</v>
       </c>
       <c r="E598" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E202, ",", F202, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,65);</v>
       </c>
       <c r="I598" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I202, ",", J202, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,65);</v>
       </c>
       <c r="M598" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M202, ",", N202, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,65);</v>
       </c>
     </row>
     <row r="599" spans="1:13">
       <c r="A599" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A203, ",", B203, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,40);</v>
       </c>
       <c r="E599" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E203, ",", F203, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,37);</v>
       </c>
       <c r="I599" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I203, ",", J203, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,37);</v>
       </c>
       <c r="M599" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M203, ",", N203, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,37);</v>
       </c>
     </row>
     <row r="600" spans="1:13">
       <c r="A600" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A204, ",", B204, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (21,42);</v>
       </c>
       <c r="E600" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E204, ",", F204, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,38);</v>
       </c>
       <c r="I600" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I204, ",", J204, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,38);</v>
       </c>
       <c r="M600" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M204, ",", N204, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,38);</v>
       </c>
     </row>
     <row r="601" spans="1:13">
       <c r="A601" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A205, ",", B205, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E601" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E205, ",", F205, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,43);</v>
       </c>
       <c r="I601" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I205, ",", J205, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,43);</v>
       </c>
       <c r="M601" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M205, ",", N205, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,43);</v>
       </c>
     </row>
     <row r="602" spans="1:13">
       <c r="A602" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A206, ",", B206, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E602" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E206, ",", F206, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,44);</v>
       </c>
       <c r="I602" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I206, ",", J206, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,44);</v>
       </c>
       <c r="M602" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M206, ",", N206, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,44);</v>
       </c>
     </row>
     <row r="603" spans="1:13">
       <c r="A603" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A207, ",", B207, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E603" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E207, ",", F207, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,45);</v>
       </c>
       <c r="I603" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I207, ",", J207, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,45);</v>
       </c>
       <c r="M603" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M207, ",", N207, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,45);</v>
       </c>
     </row>
     <row r="604" spans="1:13">
       <c r="A604" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A208, ",", B208, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E604" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E208, ",", F208, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,51);</v>
       </c>
       <c r="I604" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I208, ",", J208, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,51);</v>
       </c>
       <c r="M604" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M208, ",", N208, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,51);</v>
       </c>
     </row>
     <row r="605" spans="1:13">
       <c r="A605" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A209, ",", B209, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E605" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E209, ",", F209, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,56);</v>
       </c>
       <c r="I605" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I209, ",", J209, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,56);</v>
       </c>
       <c r="M605" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M209, ",", N209, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,56);</v>
       </c>
     </row>
     <row r="606" spans="1:13">
       <c r="A606" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A210, ",", B210, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E606" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E210, ",", F210, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,58);</v>
       </c>
       <c r="I606" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I210, ",", J210, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,58);</v>
       </c>
       <c r="M606" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M210, ",", N210, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,58);</v>
       </c>
     </row>
     <row r="607" spans="1:13">
       <c r="A607" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A211, ",", B211, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E607" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E211, ",", F211, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,40);</v>
       </c>
       <c r="I607" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I211, ",", J211, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,40);</v>
       </c>
       <c r="M607" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M211, ",", N211, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,40);</v>
       </c>
     </row>
     <row r="608" spans="1:13">
       <c r="A608" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A212, ",", B212, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E608" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E212, ",", F212, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,42);</v>
       </c>
       <c r="I608" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I212, ",", J212, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,42);</v>
       </c>
       <c r="M608" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M212, ",", N212, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,42);</v>
       </c>
     </row>
     <row r="609" spans="1:13">
       <c r="A609" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A213, ",", B213, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E609" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E213, ",", F213, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (22,66);</v>
       </c>
       <c r="I609" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I213, ",", J213, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (23,66);</v>
       </c>
       <c r="M609" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M213, ",", N213, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (24,66);</v>
       </c>
     </row>
     <row r="610" spans="1:13">
       <c r="A610" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A214, ",", B214, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E610" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E214, ",", F214, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I610" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I214, ",", J214, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M610" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M214, ",", N214, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="611" spans="1:13">
       <c r="A611" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A215, ",", B215, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (COMMUNICATION,);</v>
       </c>
       <c r="E611" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E215, ",", F215, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I611" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I215, ",", J215, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M611" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M215, ",", N215, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="612" spans="1:13">
       <c r="A612" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A216, ",", B216, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,12);</v>
       </c>
       <c r="E612" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E216, ",", F216, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,12);</v>
       </c>
       <c r="I612" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I216, ",", J216, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,12);</v>
       </c>
       <c r="M612" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M216, ",", N216, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,12);</v>
       </c>
     </row>
     <row r="613" spans="1:13">
       <c r="A613" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A217, ",", B217, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,14);</v>
       </c>
       <c r="E613" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E217, ",", F217, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,14);</v>
       </c>
       <c r="I613" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I217, ",", J217, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,14);</v>
       </c>
       <c r="M613" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M217, ",", N217, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,14);</v>
       </c>
     </row>
     <row r="614" spans="1:13">
       <c r="A614" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A218, ",", B218, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,15);</v>
       </c>
       <c r="E614" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E218, ",", F218, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,15);</v>
       </c>
       <c r="I614" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I218, ",", J218, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,15);</v>
       </c>
       <c r="M614" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M218, ",", N218, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,15);</v>
       </c>
     </row>
     <row r="615" spans="1:13">
       <c r="A615" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A219, ",", B219, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,16);</v>
       </c>
       <c r="E615" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E219, ",", F219, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,16);</v>
       </c>
       <c r="I615" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I219, ",", J219, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,16);</v>
       </c>
       <c r="M615" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M219, ",", N219, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,16);</v>
       </c>
     </row>
     <row r="616" spans="1:13">
       <c r="A616" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A220, ",", B220, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,18);</v>
       </c>
       <c r="E616" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E220, ",", F220, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,18);</v>
       </c>
       <c r="I616" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I220, ",", J220, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,18);</v>
       </c>
       <c r="M616" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M220, ",", N220, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,18);</v>
       </c>
     </row>
     <row r="617" spans="1:13">
       <c r="A617" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A221, ",", B221, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,19);</v>
       </c>
       <c r="E617" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E221, ",", F221, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,19);</v>
       </c>
       <c r="I617" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I221, ",", J221, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,19);</v>
       </c>
       <c r="M617" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M221, ",", N221, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,19);</v>
       </c>
     </row>
     <row r="618" spans="1:13">
       <c r="A618" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A222, ",", B222, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,20);</v>
       </c>
       <c r="E618" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E222, ",", F222, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,20);</v>
       </c>
       <c r="I618" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I222, ",", J222, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,20);</v>
       </c>
       <c r="M618" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M222, ",", N222, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,20);</v>
       </c>
     </row>
     <row r="619" spans="1:13">
       <c r="A619" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A223, ",", B223, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,21);</v>
       </c>
       <c r="E619" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E223, ",", F223, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,21);</v>
       </c>
       <c r="I619" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I223, ",", J223, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,21);</v>
       </c>
       <c r="M619" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M223, ",", N223, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,21);</v>
       </c>
     </row>
     <row r="620" spans="1:13">
       <c r="A620" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A224, ",", B224, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,22);</v>
       </c>
       <c r="E620" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E224, ",", F224, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,22);</v>
       </c>
       <c r="I620" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I224, ",", J224, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,22);</v>
       </c>
       <c r="M620" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M224, ",", N224, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,22);</v>
       </c>
     </row>
     <row r="621" spans="1:13">
       <c r="A621" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A225, ",", B225, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,23);</v>
       </c>
       <c r="E621" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E225, ",", F225, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,23);</v>
       </c>
       <c r="I621" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I225, ",", J225, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,23);</v>
       </c>
       <c r="M621" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M225, ",", N225, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,23);</v>
       </c>
     </row>
     <row r="622" spans="1:13">
       <c r="A622" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A226, ",", B226, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,24);</v>
       </c>
       <c r="E622" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E226, ",", F226, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,24);</v>
       </c>
       <c r="I622" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I226, ",", J226, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,24);</v>
       </c>
       <c r="M622" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M226, ",", N226, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,24);</v>
       </c>
     </row>
     <row r="623" spans="1:13">
       <c r="A623" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A227, ",", B227, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,25);</v>
       </c>
       <c r="E623" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E227, ",", F227, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,25);</v>
       </c>
       <c r="I623" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I227, ",", J227, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,25);</v>
       </c>
       <c r="M623" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M227, ",", N227, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,25);</v>
       </c>
     </row>
     <row r="624" spans="1:13">
       <c r="A624" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A228, ",", B228, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,26);</v>
       </c>
       <c r="E624" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E228, ",", F228, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,26);</v>
       </c>
       <c r="I624" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I228, ",", J228, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,26);</v>
       </c>
       <c r="M624" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M228, ",", N228, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,26);</v>
       </c>
     </row>
     <row r="625" spans="1:13">
       <c r="A625" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A229, ",", B229, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,27);</v>
       </c>
       <c r="E625" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E229, ",", F229, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,27);</v>
       </c>
       <c r="I625" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I229, ",", J229, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,27);</v>
       </c>
       <c r="M625" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M229, ",", N229, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,27);</v>
       </c>
     </row>
     <row r="626" spans="1:13">
       <c r="A626" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A230, ",", B230, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,28);</v>
       </c>
       <c r="E626" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E230, ",", F230, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,28);</v>
       </c>
       <c r="I626" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I230, ",", J230, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,28);</v>
       </c>
       <c r="M626" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M230, ",", N230, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,28);</v>
       </c>
     </row>
     <row r="627" spans="1:13">
       <c r="A627" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A231, ",", B231, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,29);</v>
       </c>
       <c r="E627" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E231, ",", F231, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,29);</v>
       </c>
       <c r="I627" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I231, ",", J231, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,29);</v>
       </c>
       <c r="M627" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M231, ",", N231, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,29);</v>
       </c>
     </row>
     <row r="628" spans="1:13">
       <c r="A628" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A232, ",", B232, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,30);</v>
       </c>
       <c r="E628" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E232, ",", F232, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,30);</v>
       </c>
       <c r="I628" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I232, ",", J232, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,30);</v>
       </c>
       <c r="M628" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M232, ",", N232, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,30);</v>
       </c>
     </row>
     <row r="629" spans="1:13">
       <c r="A629" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A233, ",", B233, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,31);</v>
       </c>
       <c r="E629" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E233, ",", F233, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,31);</v>
       </c>
       <c r="I629" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I233, ",", J233, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,31);</v>
       </c>
       <c r="M629" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M233, ",", N233, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,31);</v>
       </c>
     </row>
     <row r="630" spans="1:13">
       <c r="A630" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A234, ",", B234, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,32);</v>
       </c>
       <c r="E630" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E234, ",", F234, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,32);</v>
       </c>
       <c r="I630" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I234, ",", J234, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,32);</v>
       </c>
       <c r="M630" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M234, ",", N234, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,32);</v>
       </c>
     </row>
     <row r="631" spans="1:13">
       <c r="A631" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A235, ",", B235, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,35);</v>
       </c>
       <c r="E631" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E235, ",", F235, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,35);</v>
       </c>
       <c r="I631" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I235, ",", J235, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,35);</v>
       </c>
       <c r="M631" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M235, ",", N235, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,35);</v>
       </c>
     </row>
     <row r="632" spans="1:13">
       <c r="A632" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A236, ",", B236, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,36);</v>
       </c>
       <c r="E632" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E236, ",", F236, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,36);</v>
       </c>
       <c r="I632" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I236, ",", J236, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,36);</v>
       </c>
       <c r="M632" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M236, ",", N236, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,36);</v>
       </c>
     </row>
     <row r="633" spans="1:13">
       <c r="A633" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A237, ",", B237, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,59);</v>
       </c>
       <c r="E633" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E237, ",", F237, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,59);</v>
       </c>
       <c r="I633" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I237, ",", J237, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,59);</v>
       </c>
       <c r="M633" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M237, ",", N237, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,59);</v>
       </c>
     </row>
     <row r="634" spans="1:13">
       <c r="A634" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A238, ",", B238, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,60);</v>
       </c>
       <c r="E634" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E238, ",", F238, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,60);</v>
       </c>
       <c r="I634" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I238, ",", J238, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,60);</v>
       </c>
       <c r="M634" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M238, ",", N238, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,60);</v>
       </c>
     </row>
     <row r="635" spans="1:13">
       <c r="A635" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A239, ",", B239, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,63);</v>
       </c>
       <c r="E635" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E239, ",", F239, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,63);</v>
       </c>
       <c r="I635" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I239, ",", J239, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,63);</v>
       </c>
       <c r="M635" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M239, ",", N239, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,63);</v>
       </c>
     </row>
     <row r="636" spans="1:13">
       <c r="A636" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A240, ",", B240, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (25,65);</v>
       </c>
       <c r="E636" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E240, ",", F240, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,65);</v>
       </c>
       <c r="I636" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I240, ",", J240, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,65);</v>
       </c>
       <c r="M636" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M240, ",", N240, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,65);</v>
       </c>
     </row>
     <row r="637" spans="1:13">
       <c r="A637" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A241, ",", B241, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E637" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E241, ",", F241, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,37);</v>
       </c>
       <c r="I637" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I241, ",", J241, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,37);</v>
       </c>
       <c r="M637" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M241, ",", N241, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,37);</v>
       </c>
     </row>
     <row r="638" spans="1:13">
       <c r="A638" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A242, ",", B242, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E638" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E242, ",", F242, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,38);</v>
       </c>
       <c r="I638" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I242, ",", J242, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,38);</v>
       </c>
       <c r="M638" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M242, ",", N242, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,38);</v>
       </c>
     </row>
     <row r="639" spans="1:13">
       <c r="A639" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A243, ",", B243, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E639" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E243, ",", F243, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,43);</v>
       </c>
       <c r="I639" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I243, ",", J243, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,43);</v>
       </c>
       <c r="M639" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M243, ",", N243, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,43);</v>
       </c>
     </row>
     <row r="640" spans="1:13">
       <c r="A640" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A244, ",", B244, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E640" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E244, ",", F244, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,44);</v>
       </c>
       <c r="I640" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I244, ",", J244, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,44);</v>
       </c>
       <c r="M640" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M244, ",", N244, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,44);</v>
       </c>
     </row>
     <row r="641" spans="1:13">
       <c r="A641" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A245, ",", B245, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E641" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E245, ",", F245, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,45);</v>
       </c>
       <c r="I641" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I245, ",", J245, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,45);</v>
       </c>
       <c r="M641" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M245, ",", N245, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,45);</v>
       </c>
     </row>
     <row r="642" spans="1:13">
       <c r="A642" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A246, ",", B246, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E642" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E246, ",", F246, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,51);</v>
       </c>
       <c r="I642" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I246, ",", J246, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,51);</v>
       </c>
       <c r="M642" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M246, ",", N246, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,51);</v>
       </c>
     </row>
     <row r="643" spans="1:13">
       <c r="A643" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A247, ",", B247, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E643" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E247, ",", F247, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,56);</v>
       </c>
       <c r="I643" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I247, ",", J247, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,56);</v>
       </c>
       <c r="M643" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M247, ",", N247, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,56);</v>
       </c>
     </row>
     <row r="644" spans="1:13">
       <c r="A644" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A248, ",", B248, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E644" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E248, ",", F248, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,58);</v>
       </c>
       <c r="I644" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I248, ",", J248, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,58);</v>
       </c>
       <c r="M644" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M248, ",", N248, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,58);</v>
       </c>
     </row>
     <row r="645" spans="1:13">
       <c r="A645" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A249, ",", B249, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E645" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E249, ",", F249, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (26,41);</v>
       </c>
       <c r="I645" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I249, ",", J249, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (27,41);</v>
       </c>
       <c r="M645" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M249, ",", N249, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (28,41);</v>
       </c>
     </row>
     <row r="646" spans="1:13">
       <c r="A646" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A250, ",", B250, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (INDUSTRY,);</v>
       </c>
       <c r="E646" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E250, ",", F250, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I646" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I250, ",", J250, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M646" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M250, ",", N250, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="647" spans="1:13">
       <c r="A647" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A251, ",", B251, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,12);</v>
       </c>
       <c r="E647" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E251, ",", F251, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,12);</v>
       </c>
       <c r="I647" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I251, ",", J251, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,12);</v>
       </c>
       <c r="M647" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M251, ",", N251, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,12);</v>
       </c>
     </row>
     <row r="648" spans="1:13">
       <c r="A648" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A252, ",", B252, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,14);</v>
       </c>
       <c r="E648" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E252, ",", F252, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,14);</v>
       </c>
       <c r="I648" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I252, ",", J252, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,14);</v>
       </c>
       <c r="M648" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M252, ",", N252, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,14);</v>
       </c>
     </row>
     <row r="649" spans="1:13">
       <c r="A649" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A253, ",", B253, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,15);</v>
       </c>
       <c r="E649" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E253, ",", F253, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,15);</v>
       </c>
       <c r="I649" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I253, ",", J253, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,15);</v>
       </c>
       <c r="M649" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M253, ",", N253, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,15);</v>
       </c>
     </row>
     <row r="650" spans="1:13">
       <c r="A650" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A254, ",", B254, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,16);</v>
       </c>
       <c r="E650" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E254, ",", F254, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,16);</v>
       </c>
       <c r="I650" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I254, ",", J254, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,16);</v>
       </c>
       <c r="M650" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M254, ",", N254, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,16);</v>
       </c>
     </row>
     <row r="651" spans="1:13">
       <c r="A651" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A255, ",", B255, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,18);</v>
       </c>
       <c r="E651" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E255, ",", F255, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,18);</v>
       </c>
       <c r="I651" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I255, ",", J255, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,18);</v>
       </c>
       <c r="M651" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M255, ",", N255, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,18);</v>
       </c>
     </row>
     <row r="652" spans="1:13">
       <c r="A652" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A256, ",", B256, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,19);</v>
       </c>
       <c r="E652" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E256, ",", F256, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,19);</v>
       </c>
       <c r="I652" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I256, ",", J256, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,19);</v>
       </c>
       <c r="M652" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M256, ",", N256, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,19);</v>
       </c>
     </row>
     <row r="653" spans="1:13">
       <c r="A653" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A257, ",", B257, ");")</f>
+        <f t="shared" si="12"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,20);</v>
       </c>
       <c r="E653" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E257, ",", F257, ");")</f>
+        <f t="shared" si="13"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,20);</v>
       </c>
       <c r="I653" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I257, ",", J257, ");")</f>
+        <f t="shared" si="14"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,20);</v>
       </c>
       <c r="M653" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M257, ",", N257, ");")</f>
+        <f t="shared" si="15"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,20);</v>
       </c>
     </row>
     <row r="654" spans="1:13">
       <c r="A654" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A258, ",", B258, ");")</f>
+        <f t="shared" ref="A654:A717" si="16">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A258, ",", B258, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,21);</v>
       </c>
       <c r="E654" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E258, ",", F258, ");")</f>
+        <f t="shared" ref="E654:E717" si="17">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E258, ",", F258, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,21);</v>
       </c>
       <c r="I654" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I258, ",", J258, ");")</f>
+        <f t="shared" ref="I654:I717" si="18">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I258, ",", J258, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,21);</v>
       </c>
       <c r="M654" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M258, ",", N258, ");")</f>
+        <f t="shared" ref="M654:M717" si="19">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M258, ",", N258, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,21);</v>
       </c>
     </row>
     <row r="655" spans="1:13">
       <c r="A655" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A259, ",", B259, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,22);</v>
       </c>
       <c r="E655" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E259, ",", F259, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,22);</v>
       </c>
       <c r="I655" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I259, ",", J259, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,22);</v>
       </c>
       <c r="M655" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M259, ",", N259, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,22);</v>
       </c>
     </row>
     <row r="656" spans="1:13">
       <c r="A656" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A260, ",", B260, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,23);</v>
       </c>
       <c r="E656" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E260, ",", F260, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,23);</v>
       </c>
       <c r="I656" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I260, ",", J260, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,23);</v>
       </c>
       <c r="M656" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M260, ",", N260, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,23);</v>
       </c>
     </row>
     <row r="657" spans="1:13">
       <c r="A657" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A261, ",", B261, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,24);</v>
       </c>
       <c r="E657" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E261, ",", F261, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,24);</v>
       </c>
       <c r="I657" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I261, ",", J261, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,24);</v>
       </c>
       <c r="M657" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M261, ",", N261, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,24);</v>
       </c>
     </row>
     <row r="658" spans="1:13">
       <c r="A658" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A262, ",", B262, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,25);</v>
       </c>
       <c r="E658" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E262, ",", F262, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,25);</v>
       </c>
       <c r="I658" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I262, ",", J262, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,25);</v>
       </c>
       <c r="M658" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M262, ",", N262, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,25);</v>
       </c>
     </row>
     <row r="659" spans="1:13">
       <c r="A659" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A263, ",", B263, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,26);</v>
       </c>
       <c r="E659" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E263, ",", F263, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,26);</v>
       </c>
       <c r="I659" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I263, ",", J263, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,26);</v>
       </c>
       <c r="M659" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M263, ",", N263, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,26);</v>
       </c>
     </row>
     <row r="660" spans="1:13">
       <c r="A660" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A264, ",", B264, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,27);</v>
       </c>
       <c r="E660" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E264, ",", F264, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,27);</v>
       </c>
       <c r="I660" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I264, ",", J264, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,27);</v>
       </c>
       <c r="M660" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M264, ",", N264, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,27);</v>
       </c>
     </row>
     <row r="661" spans="1:13">
       <c r="A661" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A265, ",", B265, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,28);</v>
       </c>
       <c r="E661" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E265, ",", F265, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,28);</v>
       </c>
       <c r="I661" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I265, ",", J265, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,28);</v>
       </c>
       <c r="M661" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M265, ",", N265, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,28);</v>
       </c>
     </row>
     <row r="662" spans="1:13">
       <c r="A662" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A266, ",", B266, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,29);</v>
       </c>
       <c r="E662" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E266, ",", F266, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,29);</v>
       </c>
       <c r="I662" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I266, ",", J266, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,29);</v>
       </c>
       <c r="M662" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M266, ",", N266, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,29);</v>
       </c>
     </row>
     <row r="663" spans="1:13">
       <c r="A663" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A267, ",", B267, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,30);</v>
       </c>
       <c r="E663" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E267, ",", F267, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,30);</v>
       </c>
       <c r="I663" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I267, ",", J267, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,30);</v>
       </c>
       <c r="M663" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M267, ",", N267, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,30);</v>
       </c>
     </row>
     <row r="664" spans="1:13">
       <c r="A664" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A268, ",", B268, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,31);</v>
       </c>
       <c r="E664" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E268, ",", F268, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,31);</v>
       </c>
       <c r="I664" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I268, ",", J268, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,31);</v>
       </c>
       <c r="M664" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M268, ",", N268, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,31);</v>
       </c>
     </row>
     <row r="665" spans="1:13">
       <c r="A665" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A269, ",", B269, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,32);</v>
       </c>
       <c r="E665" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E269, ",", F269, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,32);</v>
       </c>
       <c r="I665" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I269, ",", J269, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,32);</v>
       </c>
       <c r="M665" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M269, ",", N269, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,32);</v>
       </c>
     </row>
     <row r="666" spans="1:13">
       <c r="A666" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A270, ",", B270, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,35);</v>
       </c>
       <c r="E666" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E270, ",", F270, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,35);</v>
       </c>
       <c r="I666" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I270, ",", J270, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,35);</v>
       </c>
       <c r="M666" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M270, ",", N270, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,35);</v>
       </c>
     </row>
     <row r="667" spans="1:13">
       <c r="A667" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A271, ",", B271, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,36);</v>
       </c>
       <c r="E667" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E271, ",", F271, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,36);</v>
       </c>
       <c r="I667" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I271, ",", J271, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,36);</v>
       </c>
       <c r="M667" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M271, ",", N271, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,36);</v>
       </c>
     </row>
     <row r="668" spans="1:13">
       <c r="A668" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A272, ",", B272, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,59);</v>
       </c>
       <c r="E668" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E272, ",", F272, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,59);</v>
       </c>
       <c r="I668" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I272, ",", J272, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,59);</v>
       </c>
       <c r="M668" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M272, ",", N272, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,59);</v>
       </c>
     </row>
     <row r="669" spans="1:13">
       <c r="A669" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A273, ",", B273, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,60);</v>
       </c>
       <c r="E669" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E273, ",", F273, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,60);</v>
       </c>
       <c r="I669" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I273, ",", J273, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,60);</v>
       </c>
       <c r="M669" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M273, ",", N273, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,60);</v>
       </c>
     </row>
     <row r="670" spans="1:13">
       <c r="A670" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A274, ",", B274, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,63);</v>
       </c>
       <c r="E670" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E274, ",", F274, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,63);</v>
       </c>
       <c r="I670" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I274, ",", J274, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,63);</v>
       </c>
       <c r="M670" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M274, ",", N274, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,63);</v>
       </c>
     </row>
     <row r="671" spans="1:13">
       <c r="A671" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A275, ",", B275, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (29,65);</v>
       </c>
       <c r="E671" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E275, ",", F275, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,65);</v>
       </c>
       <c r="I671" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I275, ",", J275, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,65);</v>
       </c>
       <c r="M671" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M275, ",", N275, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,65);</v>
       </c>
     </row>
     <row r="672" spans="1:13">
       <c r="A672" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A276, ",", B276, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E672" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E276, ",", F276, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,37);</v>
       </c>
       <c r="I672" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I276, ",", J276, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,37);</v>
       </c>
       <c r="M672" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M276, ",", N276, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,37);</v>
       </c>
     </row>
     <row r="673" spans="1:13">
       <c r="A673" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A277, ",", B277, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E673" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E277, ",", F277, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,38);</v>
       </c>
       <c r="I673" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I277, ",", J277, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,38);</v>
       </c>
       <c r="M673" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M277, ",", N277, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,38);</v>
       </c>
     </row>
     <row r="674" spans="1:13">
       <c r="A674" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A278, ",", B278, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E674" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E278, ",", F278, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,43);</v>
       </c>
       <c r="I674" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I278, ",", J278, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,43);</v>
       </c>
       <c r="M674" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M278, ",", N278, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,43);</v>
       </c>
     </row>
     <row r="675" spans="1:13">
       <c r="A675" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A279, ",", B279, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E675" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E279, ",", F279, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,44);</v>
       </c>
       <c r="I675" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I279, ",", J279, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,44);</v>
       </c>
       <c r="M675" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M279, ",", N279, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,44);</v>
       </c>
     </row>
     <row r="676" spans="1:13">
       <c r="A676" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A280, ",", B280, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E676" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E280, ",", F280, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,45);</v>
       </c>
       <c r="I676" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I280, ",", J280, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,45);</v>
       </c>
       <c r="M676" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M280, ",", N280, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,45);</v>
       </c>
     </row>
     <row r="677" spans="1:13">
       <c r="A677" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A281, ",", B281, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E677" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E281, ",", F281, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,51);</v>
       </c>
       <c r="I677" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I281, ",", J281, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,51);</v>
       </c>
       <c r="M677" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M281, ",", N281, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,51);</v>
       </c>
     </row>
     <row r="678" spans="1:13">
       <c r="A678" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A282, ",", B282, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E678" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E282, ",", F282, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,56);</v>
       </c>
       <c r="I678" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I282, ",", J282, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,56);</v>
       </c>
       <c r="M678" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M282, ",", N282, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,56);</v>
       </c>
     </row>
     <row r="679" spans="1:13">
       <c r="A679" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A283, ",", B283, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E679" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E283, ",", F283, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,58);</v>
       </c>
       <c r="I679" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I283, ",", J283, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,58);</v>
       </c>
       <c r="M679" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M283, ",", N283, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,58);</v>
       </c>
     </row>
     <row r="680" spans="1:13">
       <c r="A680" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A284, ",", B284, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E680" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E284, ",", F284, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (30,47);</v>
       </c>
       <c r="I680" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I284, ",", J284, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (31,47);</v>
       </c>
       <c r="M680" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M284, ",", N284, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (32,47);</v>
       </c>
     </row>
     <row r="681" spans="1:13">
       <c r="A681" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A285, ",", B285, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E681" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E285, ",", F285, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I681" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I285, ",", J285, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M681" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M285, ",", N285, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="682" spans="1:13">
       <c r="A682" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A286, ",", B286, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (DEFENCE_SYSTEM,);</v>
       </c>
       <c r="E682" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E286, ",", F286, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I682" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I286, ",", J286, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M682" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M286, ",", N286, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="683" spans="1:13">
       <c r="A683" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A287, ",", B287, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,12);</v>
       </c>
       <c r="E683" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E287, ",", F287, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,12);</v>
       </c>
       <c r="I683" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I287, ",", J287, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,12);</v>
       </c>
       <c r="M683" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M287, ",", N287, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,12);</v>
       </c>
     </row>
     <row r="684" spans="1:13">
       <c r="A684" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A288, ",", B288, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,14);</v>
       </c>
       <c r="E684" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E288, ",", F288, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,14);</v>
       </c>
       <c r="I684" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I288, ",", J288, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,14);</v>
       </c>
       <c r="M684" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M288, ",", N288, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,14);</v>
       </c>
     </row>
     <row r="685" spans="1:13">
       <c r="A685" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A289, ",", B289, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,15);</v>
       </c>
       <c r="E685" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E289, ",", F289, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,15);</v>
       </c>
       <c r="I685" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I289, ",", J289, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,15);</v>
       </c>
       <c r="M685" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M289, ",", N289, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,15);</v>
       </c>
     </row>
     <row r="686" spans="1:13">
       <c r="A686" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A290, ",", B290, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,16);</v>
       </c>
       <c r="E686" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E290, ",", F290, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,16);</v>
       </c>
       <c r="I686" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I290, ",", J290, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,16);</v>
       </c>
       <c r="M686" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M290, ",", N290, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,16);</v>
       </c>
     </row>
     <row r="687" spans="1:13">
       <c r="A687" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A291, ",", B291, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,18);</v>
       </c>
       <c r="E687" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E291, ",", F291, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,18);</v>
       </c>
       <c r="I687" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I291, ",", J291, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,18);</v>
       </c>
       <c r="M687" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M291, ",", N291, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,18);</v>
       </c>
     </row>
     <row r="688" spans="1:13">
       <c r="A688" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A292, ",", B292, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,19);</v>
       </c>
       <c r="E688" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E292, ",", F292, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,19);</v>
       </c>
       <c r="I688" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I292, ",", J292, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,19);</v>
       </c>
       <c r="M688" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M292, ",", N292, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,19);</v>
       </c>
     </row>
     <row r="689" spans="1:13">
       <c r="A689" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A293, ",", B293, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,20);</v>
       </c>
       <c r="E689" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E293, ",", F293, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,20);</v>
       </c>
       <c r="I689" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I293, ",", J293, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,20);</v>
       </c>
       <c r="M689" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M293, ",", N293, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,20);</v>
       </c>
     </row>
     <row r="690" spans="1:13">
       <c r="A690" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A294, ",", B294, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,21);</v>
       </c>
       <c r="E690" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E294, ",", F294, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,21);</v>
       </c>
       <c r="I690" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I294, ",", J294, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,21);</v>
       </c>
       <c r="M690" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M294, ",", N294, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,21);</v>
       </c>
     </row>
     <row r="691" spans="1:13">
       <c r="A691" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A295, ",", B295, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,22);</v>
       </c>
       <c r="E691" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E295, ",", F295, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,22);</v>
       </c>
       <c r="I691" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I295, ",", J295, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,22);</v>
       </c>
       <c r="M691" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M295, ",", N295, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,22);</v>
       </c>
     </row>
     <row r="692" spans="1:13">
       <c r="A692" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A296, ",", B296, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,23);</v>
       </c>
       <c r="E692" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E296, ",", F296, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,23);</v>
       </c>
       <c r="I692" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I296, ",", J296, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,23);</v>
       </c>
       <c r="M692" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M296, ",", N296, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,23);</v>
       </c>
     </row>
     <row r="693" spans="1:13">
       <c r="A693" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A297, ",", B297, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,24);</v>
       </c>
       <c r="E693" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E297, ",", F297, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,24);</v>
       </c>
       <c r="I693" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I297, ",", J297, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,24);</v>
       </c>
       <c r="M693" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M297, ",", N297, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,24);</v>
       </c>
     </row>
     <row r="694" spans="1:13">
       <c r="A694" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A298, ",", B298, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,25);</v>
       </c>
       <c r="E694" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E298, ",", F298, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,25);</v>
       </c>
       <c r="I694" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I298, ",", J298, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,25);</v>
       </c>
       <c r="M694" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M298, ",", N298, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,25);</v>
       </c>
     </row>
     <row r="695" spans="1:13">
       <c r="A695" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A299, ",", B299, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,26);</v>
       </c>
       <c r="E695" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E299, ",", F299, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,26);</v>
       </c>
       <c r="I695" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I299, ",", J299, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,26);</v>
       </c>
       <c r="M695" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M299, ",", N299, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,26);</v>
       </c>
     </row>
     <row r="696" spans="1:13">
       <c r="A696" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A300, ",", B300, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,27);</v>
       </c>
       <c r="E696" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E300, ",", F300, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,27);</v>
       </c>
       <c r="I696" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I300, ",", J300, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,27);</v>
       </c>
       <c r="M696" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M300, ",", N300, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,27);</v>
       </c>
     </row>
     <row r="697" spans="1:13">
       <c r="A697" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A301, ",", B301, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,28);</v>
       </c>
       <c r="E697" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E301, ",", F301, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,28);</v>
       </c>
       <c r="I697" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I301, ",", J301, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,28);</v>
       </c>
       <c r="M697" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M301, ",", N301, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,28);</v>
       </c>
     </row>
     <row r="698" spans="1:13">
       <c r="A698" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A302, ",", B302, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,29);</v>
       </c>
       <c r="E698" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E302, ",", F302, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,29);</v>
       </c>
       <c r="I698" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I302, ",", J302, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,29);</v>
       </c>
       <c r="M698" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M302, ",", N302, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,29);</v>
       </c>
     </row>
     <row r="699" spans="1:13">
       <c r="A699" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A303, ",", B303, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,30);</v>
       </c>
       <c r="E699" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E303, ",", F303, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,30);</v>
       </c>
       <c r="I699" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I303, ",", J303, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,30);</v>
       </c>
       <c r="M699" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M303, ",", N303, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,30);</v>
       </c>
     </row>
     <row r="700" spans="1:13">
       <c r="A700" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A304, ",", B304, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,31);</v>
       </c>
       <c r="E700" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E304, ",", F304, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,31);</v>
       </c>
       <c r="I700" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I304, ",", J304, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,31);</v>
       </c>
       <c r="M700" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M304, ",", N304, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,31);</v>
       </c>
     </row>
     <row r="701" spans="1:13">
       <c r="A701" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A305, ",", B305, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,32);</v>
       </c>
       <c r="E701" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E305, ",", F305, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,32);</v>
       </c>
       <c r="I701" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I305, ",", J305, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,32);</v>
       </c>
       <c r="M701" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M305, ",", N305, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,32);</v>
       </c>
     </row>
     <row r="702" spans="1:13">
       <c r="A702" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A306, ",", B306, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,35);</v>
       </c>
       <c r="E702" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E306, ",", F306, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,35);</v>
       </c>
       <c r="I702" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I306, ",", J306, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,35);</v>
       </c>
       <c r="M702" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M306, ",", N306, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,35);</v>
       </c>
     </row>
     <row r="703" spans="1:13">
       <c r="A703" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A307, ",", B307, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,36);</v>
       </c>
       <c r="E703" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E307, ",", F307, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,36);</v>
       </c>
       <c r="I703" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I307, ",", J307, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,36);</v>
       </c>
       <c r="M703" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M307, ",", N307, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,36);</v>
       </c>
     </row>
     <row r="704" spans="1:13">
       <c r="A704" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A308, ",", B308, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,59);</v>
       </c>
       <c r="E704" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E308, ",", F308, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,59);</v>
       </c>
       <c r="I704" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I308, ",", J308, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,59);</v>
       </c>
       <c r="M704" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M308, ",", N308, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,59);</v>
       </c>
     </row>
     <row r="705" spans="1:13">
       <c r="A705" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A309, ",", B309, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,60);</v>
       </c>
       <c r="E705" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E309, ",", F309, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,60);</v>
       </c>
       <c r="I705" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I309, ",", J309, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,60);</v>
       </c>
       <c r="M705" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M309, ",", N309, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,60);</v>
       </c>
     </row>
     <row r="706" spans="1:13">
       <c r="A706" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A310, ",", B310, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,63);</v>
       </c>
       <c r="E706" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E310, ",", F310, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,63);</v>
       </c>
       <c r="I706" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I310, ",", J310, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,63);</v>
       </c>
       <c r="M706" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M310, ",", N310, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,63);</v>
       </c>
     </row>
     <row r="707" spans="1:13">
       <c r="A707" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A311, ",", B311, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,65);</v>
       </c>
       <c r="E707" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E311, ",", F311, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,65);</v>
       </c>
       <c r="I707" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I311, ",", J311, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,65);</v>
       </c>
       <c r="M707" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M311, ",", N311, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,65);</v>
       </c>
     </row>
     <row r="708" spans="1:13">
       <c r="A708" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A312, ",", B312, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,49);</v>
       </c>
       <c r="E708" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E312, ",", F312, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,37);</v>
       </c>
       <c r="I708" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I312, ",", J312, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,37);</v>
       </c>
       <c r="M708" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M312, ",", N312, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,37);</v>
       </c>
     </row>
     <row r="709" spans="1:13">
       <c r="A709" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A313, ",", B313, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (33,50);</v>
       </c>
       <c r="E709" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E313, ",", F313, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,38);</v>
       </c>
       <c r="I709" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I313, ",", J313, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,38);</v>
       </c>
       <c r="M709" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M313, ",", N313, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,38);</v>
       </c>
     </row>
     <row r="710" spans="1:13">
       <c r="A710" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A314, ",", B314, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E710" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E314, ",", F314, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,43);</v>
       </c>
       <c r="I710" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I314, ",", J314, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,43);</v>
       </c>
       <c r="M710" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M314, ",", N314, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,43);</v>
       </c>
     </row>
     <row r="711" spans="1:13">
       <c r="A711" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A315, ",", B315, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E711" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E315, ",", F315, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,44);</v>
       </c>
       <c r="I711" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I315, ",", J315, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,44);</v>
       </c>
       <c r="M711" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M315, ",", N315, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,44);</v>
       </c>
     </row>
     <row r="712" spans="1:13">
       <c r="A712" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A316, ",", B316, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E712" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E316, ",", F316, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,45);</v>
       </c>
       <c r="I712" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I316, ",", J316, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,45);</v>
       </c>
       <c r="M712" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M316, ",", N316, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,45);</v>
       </c>
     </row>
     <row r="713" spans="1:13">
       <c r="A713" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A317, ",", B317, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E713" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E317, ",", F317, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,51);</v>
       </c>
       <c r="I713" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I317, ",", J317, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,51);</v>
       </c>
       <c r="M713" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M317, ",", N317, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,51);</v>
       </c>
     </row>
     <row r="714" spans="1:13">
       <c r="A714" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A318, ",", B318, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E714" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E318, ",", F318, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,56);</v>
       </c>
       <c r="I714" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I318, ",", J318, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,56);</v>
       </c>
       <c r="M714" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M318, ",", N318, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,56);</v>
       </c>
     </row>
     <row r="715" spans="1:13">
       <c r="A715" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A319, ",", B319, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E715" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E319, ",", F319, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,58);</v>
       </c>
       <c r="I715" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I319, ",", J319, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,58);</v>
       </c>
       <c r="M715" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M319, ",", N319, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,58);</v>
       </c>
     </row>
     <row r="716" spans="1:13">
       <c r="A716" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A320, ",", B320, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E716" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E320, ",", F320, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,49);</v>
       </c>
       <c r="I716" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I320, ",", J320, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,49);</v>
       </c>
       <c r="M716" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M320, ",", N320, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,49);</v>
       </c>
     </row>
     <row r="717" spans="1:13">
       <c r="A717" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A321, ",", B321, ");")</f>
+        <f t="shared" si="16"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E717" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E321, ",", F321, ");")</f>
+        <f t="shared" si="17"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (34,50);</v>
       </c>
       <c r="I717" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I321, ",", J321, ");")</f>
+        <f t="shared" si="18"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (35,50);</v>
       </c>
       <c r="M717" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M321, ",", N321, ");")</f>
+        <f t="shared" si="19"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (36,50);</v>
       </c>
     </row>
     <row r="718" spans="1:13">
       <c r="A718" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A322, ",", B322, ");")</f>
+        <f t="shared" ref="A718:A781" si="20">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A322, ",", B322, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E718" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E322, ",", F322, ");")</f>
+        <f t="shared" ref="E718:E781" si="21">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E322, ",", F322, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I718" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I322, ",", J322, ");")</f>
+        <f t="shared" ref="I718:I781" si="22">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I322, ",", J322, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M718" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M322, ",", N322, ");")</f>
+        <f t="shared" ref="M718:M781" si="23">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M322, ",", N322, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="719" spans="1:13">
       <c r="A719" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A323, ",", B323, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (IMPACT_ON_PUBLIC_PERCEPTION,);</v>
       </c>
       <c r="E719" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E323, ",", F323, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I719" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I323, ",", J323, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M719" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M323, ",", N323, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="720" spans="1:13">
       <c r="A720" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A324, ",", B324, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,12);</v>
       </c>
       <c r="E720" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E324, ",", F324, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,12);</v>
       </c>
       <c r="I720" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I324, ",", J324, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,12);</v>
       </c>
       <c r="M720" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M324, ",", N324, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,12);</v>
       </c>
     </row>
     <row r="721" spans="1:13">
       <c r="A721" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A325, ",", B325, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,14);</v>
       </c>
       <c r="E721" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E325, ",", F325, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,14);</v>
       </c>
       <c r="I721" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I325, ",", J325, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,14);</v>
       </c>
       <c r="M721" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M325, ",", N325, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,14);</v>
       </c>
     </row>
     <row r="722" spans="1:13">
       <c r="A722" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A326, ",", B326, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,15);</v>
       </c>
       <c r="E722" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E326, ",", F326, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,15);</v>
       </c>
       <c r="I722" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I326, ",", J326, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,15);</v>
       </c>
       <c r="M722" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M326, ",", N326, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,15);</v>
       </c>
     </row>
     <row r="723" spans="1:13">
       <c r="A723" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A327, ",", B327, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,16);</v>
       </c>
       <c r="E723" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E327, ",", F327, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,16);</v>
       </c>
       <c r="I723" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I327, ",", J327, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,16);</v>
       </c>
       <c r="M723" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M327, ",", N327, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,16);</v>
       </c>
     </row>
     <row r="724" spans="1:13">
       <c r="A724" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A328, ",", B328, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,18);</v>
       </c>
       <c r="E724" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E328, ",", F328, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,18);</v>
       </c>
       <c r="I724" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I328, ",", J328, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,18);</v>
       </c>
       <c r="M724" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M328, ",", N328, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,18);</v>
       </c>
     </row>
     <row r="725" spans="1:13">
       <c r="A725" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A329, ",", B329, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,19);</v>
       </c>
       <c r="E725" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E329, ",", F329, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,19);</v>
       </c>
       <c r="I725" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I329, ",", J329, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,19);</v>
       </c>
       <c r="M725" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M329, ",", N329, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,19);</v>
       </c>
     </row>
     <row r="726" spans="1:13">
       <c r="A726" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A330, ",", B330, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,20);</v>
       </c>
       <c r="E726" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E330, ",", F330, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,20);</v>
       </c>
       <c r="I726" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I330, ",", J330, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,20);</v>
       </c>
       <c r="M726" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M330, ",", N330, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,20);</v>
       </c>
     </row>
     <row r="727" spans="1:13">
       <c r="A727" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A331, ",", B331, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,21);</v>
       </c>
       <c r="E727" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E331, ",", F331, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,21);</v>
       </c>
       <c r="I727" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I331, ",", J331, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,21);</v>
       </c>
       <c r="M727" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M331, ",", N331, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,21);</v>
       </c>
     </row>
     <row r="728" spans="1:13">
       <c r="A728" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A332, ",", B332, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,22);</v>
       </c>
       <c r="E728" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E332, ",", F332, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,22);</v>
       </c>
       <c r="I728" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I332, ",", J332, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,22);</v>
       </c>
       <c r="M728" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M332, ",", N332, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,22);</v>
       </c>
     </row>
     <row r="729" spans="1:13">
       <c r="A729" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A333, ",", B333, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,23);</v>
       </c>
       <c r="E729" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E333, ",", F333, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,23);</v>
       </c>
       <c r="I729" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I333, ",", J333, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,23);</v>
       </c>
       <c r="M729" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M333, ",", N333, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,23);</v>
       </c>
     </row>
     <row r="730" spans="1:13">
       <c r="A730" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A334, ",", B334, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,24);</v>
       </c>
       <c r="E730" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E334, ",", F334, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,24);</v>
       </c>
       <c r="I730" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I334, ",", J334, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,24);</v>
       </c>
       <c r="M730" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M334, ",", N334, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,24);</v>
       </c>
     </row>
     <row r="731" spans="1:13">
       <c r="A731" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A335, ",", B335, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,25);</v>
       </c>
       <c r="E731" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E335, ",", F335, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,25);</v>
       </c>
       <c r="I731" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I335, ",", J335, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,25);</v>
       </c>
       <c r="M731" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M335, ",", N335, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,25);</v>
       </c>
     </row>
     <row r="732" spans="1:13">
       <c r="A732" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A336, ",", B336, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,26);</v>
       </c>
       <c r="E732" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E336, ",", F336, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,26);</v>
       </c>
       <c r="I732" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I336, ",", J336, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,26);</v>
       </c>
       <c r="M732" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M336, ",", N336, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,26);</v>
       </c>
     </row>
     <row r="733" spans="1:13">
       <c r="A733" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A337, ",", B337, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,27);</v>
       </c>
       <c r="E733" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E337, ",", F337, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,27);</v>
       </c>
       <c r="I733" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I337, ",", J337, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,27);</v>
       </c>
       <c r="M733" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M337, ",", N337, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,27);</v>
       </c>
     </row>
     <row r="734" spans="1:13">
       <c r="A734" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A338, ",", B338, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,28);</v>
       </c>
       <c r="E734" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E338, ",", F338, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,28);</v>
       </c>
       <c r="I734" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I338, ",", J338, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,28);</v>
       </c>
       <c r="M734" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M338, ",", N338, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,28);</v>
       </c>
     </row>
     <row r="735" spans="1:13">
       <c r="A735" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A339, ",", B339, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,29);</v>
       </c>
       <c r="E735" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E339, ",", F339, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,29);</v>
       </c>
       <c r="I735" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I339, ",", J339, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,29);</v>
       </c>
       <c r="M735" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M339, ",", N339, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,29);</v>
       </c>
     </row>
     <row r="736" spans="1:13">
       <c r="A736" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A340, ",", B340, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,30);</v>
       </c>
       <c r="E736" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E340, ",", F340, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,30);</v>
       </c>
       <c r="I736" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I340, ",", J340, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,30);</v>
       </c>
       <c r="M736" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M340, ",", N340, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,30);</v>
       </c>
     </row>
     <row r="737" spans="1:13">
       <c r="A737" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A341, ",", B341, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,31);</v>
       </c>
       <c r="E737" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E341, ",", F341, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,31);</v>
       </c>
       <c r="I737" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I341, ",", J341, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,31);</v>
       </c>
       <c r="M737" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M341, ",", N341, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,31);</v>
       </c>
     </row>
     <row r="738" spans="1:13">
       <c r="A738" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A342, ",", B342, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,32);</v>
       </c>
       <c r="E738" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E342, ",", F342, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,32);</v>
       </c>
       <c r="I738" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I342, ",", J342, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,32);</v>
       </c>
       <c r="M738" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M342, ",", N342, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,32);</v>
       </c>
     </row>
     <row r="739" spans="1:13">
       <c r="A739" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A343, ",", B343, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,35);</v>
       </c>
       <c r="E739" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E343, ",", F343, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,35);</v>
       </c>
       <c r="I739" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I343, ",", J343, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,35);</v>
       </c>
       <c r="M739" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M343, ",", N343, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,35);</v>
       </c>
     </row>
     <row r="740" spans="1:13">
       <c r="A740" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A344, ",", B344, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,36);</v>
       </c>
       <c r="E740" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E344, ",", F344, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,36);</v>
       </c>
       <c r="I740" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I344, ",", J344, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,36);</v>
       </c>
       <c r="M740" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M344, ",", N344, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,36);</v>
       </c>
     </row>
     <row r="741" spans="1:13">
       <c r="A741" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A345, ",", B345, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,59);</v>
       </c>
       <c r="E741" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E345, ",", F345, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,59);</v>
       </c>
       <c r="I741" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I345, ",", J345, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,59);</v>
       </c>
       <c r="M741" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M345, ",", N345, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,59);</v>
       </c>
     </row>
     <row r="742" spans="1:13">
       <c r="A742" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A346, ",", B346, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,60);</v>
       </c>
       <c r="E742" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E346, ",", F346, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,60);</v>
       </c>
       <c r="I742" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I346, ",", J346, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,60);</v>
       </c>
       <c r="M742" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M346, ",", N346, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,60);</v>
       </c>
     </row>
     <row r="743" spans="1:13">
       <c r="A743" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A347, ",", B347, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,63);</v>
       </c>
       <c r="E743" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E347, ",", F347, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,63);</v>
       </c>
       <c r="I743" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I347, ",", J347, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,63);</v>
       </c>
       <c r="M743" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M347, ",", N347, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,63);</v>
       </c>
     </row>
     <row r="744" spans="1:13">
       <c r="A744" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A348, ",", B348, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (37,65);</v>
       </c>
       <c r="E744" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E348, ",", F348, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,65);</v>
       </c>
       <c r="I744" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I348, ",", J348, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,65);</v>
       </c>
       <c r="M744" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M348, ",", N348, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,65);</v>
       </c>
     </row>
     <row r="745" spans="1:13">
       <c r="A745" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A349, ",", B349, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E745" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E349, ",", F349, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,37);</v>
       </c>
       <c r="I745" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I349, ",", J349, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,37);</v>
       </c>
       <c r="M745" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M349, ",", N349, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,37);</v>
       </c>
     </row>
     <row r="746" spans="1:13">
       <c r="A746" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A350, ",", B350, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E746" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E350, ",", F350, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,38);</v>
       </c>
       <c r="I746" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I350, ",", J350, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,38);</v>
       </c>
       <c r="M746" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M350, ",", N350, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,38);</v>
       </c>
     </row>
     <row r="747" spans="1:13">
       <c r="A747" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A351, ",", B351, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E747" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E351, ",", F351, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,43);</v>
       </c>
       <c r="I747" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I351, ",", J351, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,43);</v>
       </c>
       <c r="M747" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M351, ",", N351, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,43);</v>
       </c>
     </row>
     <row r="748" spans="1:13">
       <c r="A748" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A352, ",", B352, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E748" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E352, ",", F352, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,44);</v>
       </c>
       <c r="I748" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I352, ",", J352, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,44);</v>
       </c>
       <c r="M748" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M352, ",", N352, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,44);</v>
       </c>
     </row>
     <row r="749" spans="1:13">
       <c r="A749" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A353, ",", B353, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E749" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E353, ",", F353, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,45);</v>
       </c>
       <c r="I749" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I353, ",", J353, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,45);</v>
       </c>
       <c r="M749" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M353, ",", N353, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,45);</v>
       </c>
     </row>
     <row r="750" spans="1:13">
       <c r="A750" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A354, ",", B354, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E750" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E354, ",", F354, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,51);</v>
       </c>
       <c r="I750" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I354, ",", J354, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,51);</v>
       </c>
       <c r="M750" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M354, ",", N354, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,51);</v>
       </c>
     </row>
     <row r="751" spans="1:13">
       <c r="A751" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A355, ",", B355, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E751" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E355, ",", F355, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,56);</v>
       </c>
       <c r="I751" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I355, ",", J355, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,56);</v>
       </c>
       <c r="M751" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M355, ",", N355, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,56);</v>
       </c>
     </row>
     <row r="752" spans="1:13">
       <c r="A752" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A356, ",", B356, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E752" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E356, ",", F356, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,58);</v>
       </c>
       <c r="I752" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I356, ",", J356, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,58);</v>
       </c>
       <c r="M752" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M356, ",", N356, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,58);</v>
       </c>
     </row>
     <row r="753" spans="1:13">
       <c r="A753" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A357, ",", B357, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E753" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E357, ",", F357, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,54);</v>
       </c>
       <c r="I753" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I357, ",", J357, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,54);</v>
       </c>
       <c r="M753" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M357, ",", N357, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,54);</v>
       </c>
     </row>
     <row r="754" spans="1:13">
       <c r="A754" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A358, ",", B358, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E754" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E358, ",", F358, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,55);</v>
       </c>
       <c r="I754" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I358, ",", J358, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,55);</v>
       </c>
       <c r="M754" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M358, ",", N358, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,55);</v>
       </c>
     </row>
     <row r="755" spans="1:13">
       <c r="A755" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A359, ",", B359, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E755" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E359, ",", F359, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (38,57);</v>
       </c>
       <c r="I755" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I359, ",", J359, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (39,57);</v>
       </c>
       <c r="M755" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M359, ",", N359, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (40,57);</v>
       </c>
     </row>
     <row r="756" spans="1:13">
       <c r="A756" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A360, ",", B360, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E756" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E360, ",", F360, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I756" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I360, ",", J360, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M756" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M360, ",", N360, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="757" spans="1:13">
       <c r="A757" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A361, ",", B361, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (SPECIAL_OR_BIOMETRIC_OFFICIALS_PERSONAL_DATA,);</v>
       </c>
       <c r="E757" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E361, ",", F361, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I757" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I361, ",", J361, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M757" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M361, ",", N361, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="758" spans="1:13">
       <c r="A758" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A362, ",", B362, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,12);</v>
       </c>
       <c r="E758" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E362, ",", F362, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,12);</v>
       </c>
       <c r="I758" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I362, ",", J362, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,12);</v>
       </c>
       <c r="M758" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M362, ",", N362, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,12);</v>
       </c>
     </row>
     <row r="759" spans="1:13">
       <c r="A759" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A363, ",", B363, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,14);</v>
       </c>
       <c r="E759" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E363, ",", F363, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,14);</v>
       </c>
       <c r="I759" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I363, ",", J363, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,14);</v>
       </c>
       <c r="M759" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M363, ",", N363, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,14);</v>
       </c>
     </row>
     <row r="760" spans="1:13">
       <c r="A760" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A364, ",", B364, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,15);</v>
       </c>
       <c r="E760" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E364, ",", F364, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,15);</v>
       </c>
       <c r="I760" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I364, ",", J364, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,15);</v>
       </c>
       <c r="M760" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M364, ",", N364, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,15);</v>
       </c>
     </row>
     <row r="761" spans="1:13">
       <c r="A761" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A365, ",", B365, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,16);</v>
       </c>
       <c r="E761" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E365, ",", F365, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,16);</v>
       </c>
       <c r="I761" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I365, ",", J365, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,16);</v>
       </c>
       <c r="M761" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M365, ",", N365, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,16);</v>
       </c>
     </row>
     <row r="762" spans="1:13">
       <c r="A762" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A366, ",", B366, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,18);</v>
       </c>
       <c r="E762" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E366, ",", F366, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,18);</v>
       </c>
       <c r="I762" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I366, ",", J366, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,18);</v>
       </c>
       <c r="M762" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M366, ",", N366, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,18);</v>
       </c>
     </row>
     <row r="763" spans="1:13">
       <c r="A763" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A367, ",", B367, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,19);</v>
       </c>
       <c r="E763" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E367, ",", F367, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,19);</v>
       </c>
       <c r="I763" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I367, ",", J367, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,19);</v>
       </c>
       <c r="M763" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M367, ",", N367, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,19);</v>
       </c>
     </row>
     <row r="764" spans="1:13">
       <c r="A764" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A368, ",", B368, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,20);</v>
       </c>
       <c r="E764" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E368, ",", F368, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,20);</v>
       </c>
       <c r="I764" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I368, ",", J368, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,20);</v>
       </c>
       <c r="M764" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M368, ",", N368, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,20);</v>
       </c>
     </row>
     <row r="765" spans="1:13">
       <c r="A765" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A369, ",", B369, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,21);</v>
       </c>
       <c r="E765" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E369, ",", F369, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,21);</v>
       </c>
       <c r="I765" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I369, ",", J369, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,21);</v>
       </c>
       <c r="M765" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M369, ",", N369, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,21);</v>
       </c>
     </row>
     <row r="766" spans="1:13">
       <c r="A766" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A370, ",", B370, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,22);</v>
       </c>
       <c r="E766" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E370, ",", F370, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,22);</v>
       </c>
       <c r="I766" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I370, ",", J370, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,22);</v>
       </c>
       <c r="M766" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M370, ",", N370, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,22);</v>
       </c>
     </row>
     <row r="767" spans="1:13">
       <c r="A767" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A371, ",", B371, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,23);</v>
       </c>
       <c r="E767" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E371, ",", F371, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,23);</v>
       </c>
       <c r="I767" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I371, ",", J371, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,23);</v>
       </c>
       <c r="M767" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M371, ",", N371, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,23);</v>
       </c>
     </row>
     <row r="768" spans="1:13">
       <c r="A768" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A372, ",", B372, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,24);</v>
       </c>
       <c r="E768" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E372, ",", F372, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,24);</v>
       </c>
       <c r="I768" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I372, ",", J372, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,24);</v>
       </c>
       <c r="M768" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M372, ",", N372, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,24);</v>
       </c>
     </row>
     <row r="769" spans="1:13">
       <c r="A769" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A373, ",", B373, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,25);</v>
       </c>
       <c r="E769" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E373, ",", F373, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,25);</v>
       </c>
       <c r="I769" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I373, ",", J373, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,25);</v>
       </c>
       <c r="M769" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M373, ",", N373, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,25);</v>
       </c>
     </row>
     <row r="770" spans="1:13">
       <c r="A770" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A374, ",", B374, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,26);</v>
       </c>
       <c r="E770" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E374, ",", F374, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,26);</v>
       </c>
       <c r="I770" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I374, ",", J374, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,26);</v>
       </c>
       <c r="M770" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M374, ",", N374, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,26);</v>
       </c>
     </row>
     <row r="771" spans="1:13">
       <c r="A771" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A375, ",", B375, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,27);</v>
       </c>
       <c r="E771" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E375, ",", F375, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,27);</v>
       </c>
       <c r="I771" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I375, ",", J375, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,27);</v>
       </c>
       <c r="M771" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M375, ",", N375, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,27);</v>
       </c>
     </row>
     <row r="772" spans="1:13">
       <c r="A772" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A376, ",", B376, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,28);</v>
       </c>
       <c r="E772" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E376, ",", F376, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,28);</v>
       </c>
       <c r="I772" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I376, ",", J376, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,28);</v>
       </c>
       <c r="M772" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M376, ",", N376, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,28);</v>
       </c>
     </row>
     <row r="773" spans="1:13">
       <c r="A773" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A377, ",", B377, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,29);</v>
       </c>
       <c r="E773" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E377, ",", F377, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,29);</v>
       </c>
       <c r="I773" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I377, ",", J377, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,29);</v>
       </c>
       <c r="M773" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M377, ",", N377, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,29);</v>
       </c>
     </row>
     <row r="774" spans="1:13">
       <c r="A774" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A378, ",", B378, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,30);</v>
       </c>
       <c r="E774" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E378, ",", F378, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,30);</v>
       </c>
       <c r="I774" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I378, ",", J378, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,30);</v>
       </c>
       <c r="M774" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M378, ",", N378, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,30);</v>
       </c>
     </row>
     <row r="775" spans="1:13">
       <c r="A775" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A379, ",", B379, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,31);</v>
       </c>
       <c r="E775" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E379, ",", F379, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,31);</v>
       </c>
       <c r="I775" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I379, ",", J379, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,31);</v>
       </c>
       <c r="M775" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M379, ",", N379, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,31);</v>
       </c>
     </row>
     <row r="776" spans="1:13">
       <c r="A776" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A380, ",", B380, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,32);</v>
       </c>
       <c r="E776" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E380, ",", F380, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,32);</v>
       </c>
       <c r="I776" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I380, ",", J380, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,32);</v>
       </c>
       <c r="M776" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M380, ",", N380, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,32);</v>
       </c>
     </row>
     <row r="777" spans="1:13">
       <c r="A777" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A381, ",", B381, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,35);</v>
       </c>
       <c r="E777" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E381, ",", F381, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,35);</v>
       </c>
       <c r="I777" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I381, ",", J381, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,35);</v>
       </c>
       <c r="M777" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M381, ",", N381, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,35);</v>
       </c>
     </row>
     <row r="778" spans="1:13">
       <c r="A778" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A382, ",", B382, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,36);</v>
       </c>
       <c r="E778" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E382, ",", F382, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,36);</v>
       </c>
       <c r="I778" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I382, ",", J382, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,36);</v>
       </c>
       <c r="M778" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M382, ",", N382, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,36);</v>
       </c>
     </row>
     <row r="779" spans="1:13">
       <c r="A779" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A383, ",", B383, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,59);</v>
       </c>
       <c r="E779" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E383, ",", F383, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,59);</v>
       </c>
       <c r="I779" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I383, ",", J383, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,59);</v>
       </c>
       <c r="M779" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M383, ",", N383, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,59);</v>
       </c>
     </row>
     <row r="780" spans="1:13">
       <c r="A780" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A384, ",", B384, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,60);</v>
       </c>
       <c r="E780" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E384, ",", F384, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,60);</v>
       </c>
       <c r="I780" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I384, ",", J384, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,60);</v>
       </c>
       <c r="M780" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M384, ",", N384, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,60);</v>
       </c>
     </row>
     <row r="781" spans="1:13">
       <c r="A781" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A385, ",", B385, ");")</f>
+        <f t="shared" si="20"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,63);</v>
       </c>
       <c r="E781" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E385, ",", F385, ");")</f>
+        <f t="shared" si="21"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,63);</v>
       </c>
       <c r="I781" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I385, ",", J385, ");")</f>
+        <f t="shared" si="22"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,63);</v>
       </c>
       <c r="M781" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M385, ",", N385, ");")</f>
+        <f t="shared" si="23"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,63);</v>
       </c>
     </row>
     <row r="782" spans="1:13">
       <c r="A782" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A386, ",", B386, ");")</f>
+        <f t="shared" ref="A782:A845" si="24">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A386, ",", B386, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (41,65);</v>
       </c>
       <c r="E782" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E386, ",", F386, ");")</f>
+        <f t="shared" ref="E782:E845" si="25">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E386, ",", F386, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,65);</v>
       </c>
       <c r="I782" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I386, ",", J386, ");")</f>
+        <f t="shared" ref="I782:I845" si="26">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I386, ",", J386, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,65);</v>
       </c>
       <c r="M782" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M386, ",", N386, ");")</f>
+        <f t="shared" ref="M782:M845" si="27">_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M386, ",", N386, ");")</f>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,65);</v>
       </c>
     </row>
     <row r="783" spans="1:13">
       <c r="A783" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A387, ",", B387, ");")</f>
+        <f t="shared" si="24"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E783" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E387, ",", F387, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,37);</v>
       </c>
       <c r="I783" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I387, ",", J387, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,37);</v>
       </c>
       <c r="M783" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M387, ",", N387, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,37);</v>
       </c>
     </row>
     <row r="784" spans="1:13">
       <c r="A784" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A388, ",", B388, ");")</f>
+        <f t="shared" si="24"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E784" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E388, ",", F388, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,38);</v>
       </c>
       <c r="I784" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I388, ",", J388, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,38);</v>
       </c>
       <c r="M784" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M388, ",", N388, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,38);</v>
       </c>
     </row>
     <row r="785" spans="1:13">
       <c r="A785" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", A389, ",", B389, ");")</f>
+        <f t="shared" si="24"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="E785" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E389, ",", F389, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,43);</v>
       </c>
       <c r="I785" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I389, ",", J389, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,43);</v>
       </c>
       <c r="M785" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M389, ",", N389, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,43);</v>
       </c>
     </row>
     <row r="786" spans="1:13">
       <c r="E786" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E390, ",", F390, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,44);</v>
       </c>
       <c r="I786" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I390, ",", J390, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,44);</v>
       </c>
       <c r="M786" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M390, ",", N390, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,44);</v>
       </c>
     </row>
     <row r="787" spans="1:13">
       <c r="E787" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E391, ",", F391, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,45);</v>
       </c>
       <c r="I787" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I391, ",", J391, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,45);</v>
       </c>
       <c r="M787" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M391, ",", N391, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,45);</v>
       </c>
     </row>
     <row r="788" spans="1:13">
       <c r="E788" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E392, ",", F392, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,51);</v>
       </c>
       <c r="I788" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I392, ",", J392, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,51);</v>
       </c>
       <c r="M788" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M392, ",", N392, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,51);</v>
       </c>
     </row>
     <row r="789" spans="1:13">
       <c r="E789" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E393, ",", F393, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,56);</v>
       </c>
       <c r="I789" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I393, ",", J393, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,56);</v>
       </c>
       <c r="M789" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M393, ",", N393, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,56);</v>
       </c>
     </row>
     <row r="790" spans="1:13">
       <c r="E790" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E394, ",", F394, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,58);</v>
       </c>
       <c r="I790" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I394, ",", J394, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,58);</v>
       </c>
       <c r="M790" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M394, ",", N394, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,58);</v>
       </c>
     </row>
     <row r="791" spans="1:13">
       <c r="E791" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E395, ",", F395, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (42,62);</v>
       </c>
       <c r="I791" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I395, ",", J395, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (43,62);</v>
       </c>
       <c r="M791" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M395, ",", N395, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (44,62);</v>
       </c>
     </row>
     <row r="792" spans="1:13">
       <c r="E792" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E396, ",", F396, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I792" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I396, ",", J396, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M792" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M396, ",", N396, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
     <row r="793" spans="1:13">
       <c r="E793" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", E397, ",", F397, ");")</f>
+        <f t="shared" si="25"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="I793" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", I397, ",", J397, ");")</f>
+        <f t="shared" si="26"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
       <c r="M793" t="str">
-        <f>_xlfn.CONCAT("INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (", M397, ",", N397, ");")</f>
+        <f t="shared" si="27"/>
         <v>INSERT INTO app_kiiclass_negative_consequences  (kiiclass_id, negativeconsequence_id) VALUES (,);</v>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
     <col min="2" max="2" width="74" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="17">
       <c r="A1">
         <v>12</v>
       </c>
@@ -18089,7 +18089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="17">
       <c r="A2">
         <v>13</v>
       </c>
@@ -18103,7 +18103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="17">
       <c r="A3">
         <v>14</v>
       </c>
@@ -18117,7 +18117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="17">
       <c r="A4">
         <v>15</v>
       </c>
@@ -18131,7 +18131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="17">
       <c r="A5">
         <v>16</v>
       </c>
@@ -18145,7 +18145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="34">
       <c r="A6">
         <v>17</v>
       </c>
@@ -18159,7 +18159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" ht="17">
       <c r="A7">
         <v>18</v>
       </c>
@@ -18173,7 +18173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" ht="17">
       <c r="A8">
         <v>19</v>
       </c>
@@ -18187,7 +18187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="17">
       <c r="A9">
         <v>20</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="17">
       <c r="A10">
         <v>21</v>
       </c>
@@ -18215,7 +18215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" ht="17">
       <c r="A11">
         <v>22</v>
       </c>
@@ -18229,7 +18229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="17">
       <c r="A12">
         <v>23</v>
       </c>
@@ -18243,7 +18243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="17">
       <c r="A13">
         <v>24</v>
       </c>
@@ -18257,7 +18257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="17">
       <c r="A14">
         <v>25</v>
       </c>
@@ -18271,7 +18271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="17">
       <c r="A15">
         <v>26</v>
       </c>
@@ -18285,7 +18285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="17">
       <c r="A16">
         <v>27</v>
       </c>
@@ -18299,7 +18299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="17">
       <c r="A17">
         <v>28</v>
       </c>
@@ -18313,7 +18313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" ht="17">
       <c r="A18">
         <v>29</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" ht="34">
       <c r="A19">
         <v>30</v>
       </c>
@@ -18341,7 +18341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" ht="17">
       <c r="A20">
         <v>31</v>
       </c>
@@ -18355,7 +18355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" ht="17">
       <c r="A21">
         <v>32</v>
       </c>
@@ -18369,7 +18369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" ht="17">
       <c r="A22">
         <v>33</v>
       </c>
@@ -18383,7 +18383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" ht="34">
       <c r="A23">
         <v>34</v>
       </c>
@@ -18397,7 +18397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" ht="34">
       <c r="A24">
         <v>35</v>
       </c>
@@ -18411,7 +18411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" ht="34">
       <c r="A25">
         <v>36</v>
       </c>
